--- a/research/traditional_assets/database/data/egypt/egypt_information_services.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_information_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1919652958462386</v>
+        <v>0.1915682489305846</v>
       </c>
       <c r="C2">
-        <v>44.51820830126461</v>
+        <v>44.14117987052613</v>
       </c>
       <c r="D2">
-        <v>34.2182083012646</v>
+        <v>34.27517987052612</v>
       </c>
       <c r="E2">
-        <v>-14.8</v>
+        <v>-14.366</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4340000000000001</v>
       </c>
       <c r="G2">
         <v>10.3</v>
@@ -1451,28 +1451,28 @@
         <v>9.84</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0218302</v>
       </c>
       <c r="N2">
-        <v>9.84</v>
+        <v>9.8181698</v>
       </c>
       <c r="O2">
-        <v>2.214</v>
+        <v>2.209088205</v>
       </c>
       <c r="P2">
-        <v>7.625999999999999</v>
+        <v>7.609081594999999</v>
       </c>
       <c r="Q2">
-        <v>9.786</v>
+        <v>9.769081594999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1919652958462386</v>
+        <v>0.1931095191218026</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.027107159858777</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>450.7517109325613</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1915682489305846</v>
+        <v>0.1911712020149305</v>
       </c>
       <c r="C3">
-        <v>44.14117987052613</v>
+        <v>43.7643414656775</v>
       </c>
       <c r="D3">
-        <v>34.27517987052612</v>
+        <v>34.3323414656775</v>
       </c>
       <c r="E3">
-        <v>-14.366</v>
+        <v>-13.932</v>
       </c>
       <c r="F3">
-        <v>0.4340000000000001</v>
+        <v>0.8680000000000001</v>
       </c>
       <c r="G3">
         <v>10.3</v>
@@ -1533,28 +1533,28 @@
         <v>9.84</v>
       </c>
       <c r="M3">
-        <v>0.0218302</v>
+        <v>0.0436604</v>
       </c>
       <c r="N3">
-        <v>9.8181698</v>
+        <v>9.7963396</v>
       </c>
       <c r="O3">
-        <v>2.209088205</v>
+        <v>2.20417641</v>
       </c>
       <c r="P3">
-        <v>7.609081594999999</v>
+        <v>7.592163189999999</v>
       </c>
       <c r="Q3">
-        <v>9.769081594999999</v>
+        <v>9.752163189999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1931095191218026</v>
+        <v>0.1942770938927863</v>
       </c>
       <c r="T3">
-        <v>1.027107159858777</v>
+        <v>1.035248007877948</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>450.7517109325613</v>
+        <v>225.3758554662806</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1911712020149305</v>
+        <v>0.1907741550992765</v>
       </c>
       <c r="C4">
-        <v>43.7643414656775</v>
+        <v>43.38769403904006</v>
       </c>
       <c r="D4">
-        <v>34.3323414656775</v>
+        <v>34.38969403904006</v>
       </c>
       <c r="E4">
-        <v>-13.932</v>
+        <v>-13.498</v>
       </c>
       <c r="F4">
-        <v>0.8680000000000001</v>
+        <v>1.302</v>
       </c>
       <c r="G4">
         <v>10.3</v>
@@ -1615,28 +1615,28 @@
         <v>9.84</v>
       </c>
       <c r="M4">
-        <v>0.0436604</v>
+        <v>0.0654906</v>
       </c>
       <c r="N4">
-        <v>9.7963396</v>
+        <v>9.774509399999999</v>
       </c>
       <c r="O4">
-        <v>2.20417641</v>
+        <v>2.199264615</v>
       </c>
       <c r="P4">
-        <v>7.592163189999999</v>
+        <v>7.575244784999999</v>
       </c>
       <c r="Q4">
-        <v>9.752163189999999</v>
+        <v>9.735244784999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1942770938927863</v>
+        <v>0.1954687423703882</v>
       </c>
       <c r="T4">
-        <v>1.035248007877948</v>
+        <v>1.043556708433597</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>225.3758554662806</v>
+        <v>150.2505703108538</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1907741550992765</v>
+        <v>0.1903771081836225</v>
       </c>
       <c r="C5">
-        <v>43.38769403904006</v>
+        <v>43.01123854930926</v>
       </c>
       <c r="D5">
-        <v>34.38969403904006</v>
+        <v>34.44723854930925</v>
       </c>
       <c r="E5">
-        <v>-13.498</v>
+        <v>-13.064</v>
       </c>
       <c r="F5">
-        <v>1.302</v>
+        <v>1.736</v>
       </c>
       <c r="G5">
         <v>10.3</v>
@@ -1697,28 +1697,28 @@
         <v>9.84</v>
       </c>
       <c r="M5">
-        <v>0.0654906</v>
+        <v>0.0873208</v>
       </c>
       <c r="N5">
-        <v>9.774509399999999</v>
+        <v>9.752679199999999</v>
       </c>
       <c r="O5">
-        <v>2.199264615</v>
+        <v>2.19435282</v>
       </c>
       <c r="P5">
-        <v>7.575244784999999</v>
+        <v>7.55832638</v>
       </c>
       <c r="Q5">
-        <v>9.735244784999999</v>
+        <v>9.718326380000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1954687423703882</v>
+        <v>0.1966852168579401</v>
       </c>
       <c r="T5">
-        <v>1.043556708433597</v>
+        <v>1.052038506917489</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>150.2505703108538</v>
+        <v>112.6879277331403</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1903771081836225</v>
+        <v>0.1899800612679684</v>
       </c>
       <c r="C6">
-        <v>43.01123854930926</v>
+        <v>42.63497596160802</v>
       </c>
       <c r="D6">
-        <v>34.44723854930925</v>
+        <v>34.50497596160803</v>
       </c>
       <c r="E6">
-        <v>-13.064</v>
+        <v>-12.63</v>
       </c>
       <c r="F6">
-        <v>1.736</v>
+        <v>2.17</v>
       </c>
       <c r="G6">
         <v>10.3</v>
@@ -1779,28 +1779,28 @@
         <v>9.84</v>
       </c>
       <c r="M6">
-        <v>0.0873208</v>
+        <v>0.109151</v>
       </c>
       <c r="N6">
-        <v>9.752679199999999</v>
+        <v>9.730848999999999</v>
       </c>
       <c r="O6">
-        <v>2.19435282</v>
+        <v>2.189441025</v>
       </c>
       <c r="P6">
-        <v>7.55832638</v>
+        <v>7.541407974999999</v>
       </c>
       <c r="Q6">
-        <v>9.718326380000001</v>
+        <v>9.701407974999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1966852168579401</v>
+        <v>0.1979273013347036</v>
       </c>
       <c r="T6">
-        <v>1.052038506917489</v>
+        <v>1.060698869579989</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>112.6879277331403</v>
+        <v>90.15034218651225</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1899800612679684</v>
+        <v>0.1895830143523144</v>
       </c>
       <c r="C7">
-        <v>42.63497596160802</v>
+        <v>42.25890724754083</v>
       </c>
       <c r="D7">
-        <v>34.50497596160803</v>
+        <v>34.56290724754083</v>
       </c>
       <c r="E7">
-        <v>-12.63</v>
+        <v>-12.196</v>
       </c>
       <c r="F7">
-        <v>2.17</v>
+        <v>2.604000000000001</v>
       </c>
       <c r="G7">
         <v>10.3</v>
@@ -1861,28 +1861,28 @@
         <v>9.84</v>
       </c>
       <c r="M7">
-        <v>0.109151</v>
+        <v>0.1309812</v>
       </c>
       <c r="N7">
-        <v>9.730848999999999</v>
+        <v>9.709018799999999</v>
       </c>
       <c r="O7">
-        <v>2.189441025</v>
+        <v>2.18452923</v>
       </c>
       <c r="P7">
-        <v>7.541407974999999</v>
+        <v>7.524489569999999</v>
       </c>
       <c r="Q7">
-        <v>9.701407974999999</v>
+        <v>9.68448957</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1979273013347036</v>
+        <v>0.19919581314076</v>
       </c>
       <c r="T7">
-        <v>1.060698869579989</v>
+        <v>1.069543495277861</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>90.15034218651225</v>
+        <v>75.12528515542687</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1895830143523144</v>
+        <v>0.1891859674366604</v>
       </c>
       <c r="C8">
-        <v>42.25890724754083</v>
+        <v>41.88303338524808</v>
       </c>
       <c r="D8">
-        <v>34.56290724754083</v>
+        <v>34.62103338524808</v>
       </c>
       <c r="E8">
-        <v>-12.196</v>
+        <v>-11.762</v>
       </c>
       <c r="F8">
-        <v>2.604</v>
+        <v>3.038</v>
       </c>
       <c r="G8">
         <v>10.3</v>
@@ -1943,28 +1943,28 @@
         <v>9.84</v>
       </c>
       <c r="M8">
-        <v>0.1309812</v>
+        <v>0.1528114</v>
       </c>
       <c r="N8">
-        <v>9.709018799999999</v>
+        <v>9.687188600000001</v>
       </c>
       <c r="O8">
-        <v>2.18452923</v>
+        <v>2.179617435</v>
       </c>
       <c r="P8">
-        <v>7.524489569999999</v>
+        <v>7.507571165</v>
       </c>
       <c r="Q8">
-        <v>9.68448957</v>
+        <v>9.667571165</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.19919581314076</v>
+        <v>0.2004916047706026</v>
       </c>
       <c r="T8">
-        <v>1.069543495277861</v>
+        <v>1.078578327979989</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>75.12528515542688</v>
+        <v>64.39310156179448</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1891859674366604</v>
+        <v>0.1887889205210063</v>
       </c>
       <c r="C9">
-        <v>41.88303338524808</v>
+        <v>41.50735535946124</v>
       </c>
       <c r="D9">
-        <v>34.62103338524808</v>
+        <v>34.67935535946123</v>
       </c>
       <c r="E9">
-        <v>-11.762</v>
+        <v>-11.328</v>
       </c>
       <c r="F9">
-        <v>3.038000000000001</v>
+        <v>3.472</v>
       </c>
       <c r="G9">
         <v>10.3</v>
@@ -2025,28 +2025,28 @@
         <v>9.84</v>
       </c>
       <c r="M9">
-        <v>0.1528114</v>
+        <v>0.1746416</v>
       </c>
       <c r="N9">
-        <v>9.687188600000001</v>
+        <v>9.665358400000001</v>
       </c>
       <c r="O9">
-        <v>2.179617435</v>
+        <v>2.17470564</v>
       </c>
       <c r="P9">
-        <v>7.507571165</v>
+        <v>7.490652760000001</v>
       </c>
       <c r="Q9">
-        <v>9.667571165</v>
+        <v>9.65065276</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2004916047706026</v>
+        <v>0.2018155657837025</v>
       </c>
       <c r="T9">
-        <v>1.078578327979989</v>
+        <v>1.087809570088685</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>64.39310156179448</v>
+        <v>56.34396386657016</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1887889205210063</v>
+        <v>0.1883918736053523</v>
       </c>
       <c r="C10">
-        <v>41.50735535946124</v>
+        <v>41.13187416155839</v>
       </c>
       <c r="D10">
-        <v>34.67935535946123</v>
+        <v>34.73787416155839</v>
       </c>
       <c r="E10">
-        <v>-11.328</v>
+        <v>-10.894</v>
       </c>
       <c r="F10">
-        <v>3.472</v>
+        <v>3.906000000000001</v>
       </c>
       <c r="G10">
         <v>10.3</v>
@@ -2107,28 +2107,28 @@
         <v>9.84</v>
       </c>
       <c r="M10">
-        <v>0.1746416</v>
+        <v>0.1964718</v>
       </c>
       <c r="N10">
-        <v>9.665358400000001</v>
+        <v>9.6435282</v>
       </c>
       <c r="O10">
-        <v>2.17470564</v>
+        <v>2.169793845</v>
       </c>
       <c r="P10">
-        <v>7.490652760000001</v>
+        <v>7.473734355</v>
       </c>
       <c r="Q10">
-        <v>9.65065276</v>
+        <v>9.633734355000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2018155657837025</v>
+        <v>0.2031686248410465</v>
       </c>
       <c r="T10">
-        <v>1.087809570088685</v>
+        <v>1.097243696639329</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>56.34396386657016</v>
+        <v>50.08352343695125</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1883918736053523</v>
+        <v>0.1879948266896982</v>
       </c>
       <c r="C11">
-        <v>41.13187416155839</v>
+        <v>40.75659078962046</v>
       </c>
       <c r="D11">
-        <v>34.73787416155839</v>
+        <v>34.79659078962046</v>
       </c>
       <c r="E11">
-        <v>-10.894</v>
+        <v>-10.46</v>
       </c>
       <c r="F11">
-        <v>3.906000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="G11">
         <v>10.3</v>
@@ -2189,28 +2189,28 @@
         <v>9.84</v>
       </c>
       <c r="M11">
-        <v>0.1964718</v>
+        <v>0.218302</v>
       </c>
       <c r="N11">
-        <v>9.6435282</v>
+        <v>9.621698</v>
       </c>
       <c r="O11">
-        <v>2.169793845</v>
+        <v>2.16488205</v>
       </c>
       <c r="P11">
-        <v>7.473734355</v>
+        <v>7.45681595</v>
       </c>
       <c r="Q11">
-        <v>9.633734355000001</v>
+        <v>9.616815949999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2031686248410465</v>
+        <v>0.2045517518774425</v>
       </c>
       <c r="T11">
-        <v>1.097243696639329</v>
+        <v>1.106887470446655</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>50.08352343695125</v>
+        <v>45.07517109325614</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1879948266896982</v>
+        <v>0.1875977797740442</v>
       </c>
       <c r="C12">
-        <v>40.75659078962046</v>
+        <v>40.38150624848788</v>
       </c>
       <c r="D12">
-        <v>34.79659078962046</v>
+        <v>34.85550624848788</v>
       </c>
       <c r="E12">
-        <v>-10.46</v>
+        <v>-10.026</v>
       </c>
       <c r="F12">
-        <v>4.340000000000001</v>
+        <v>4.774000000000001</v>
       </c>
       <c r="G12">
         <v>10.3</v>
@@ -2271,28 +2271,28 @@
         <v>9.84</v>
       </c>
       <c r="M12">
-        <v>0.218302</v>
+        <v>0.2401322</v>
       </c>
       <c r="N12">
-        <v>9.621698</v>
+        <v>9.5998678</v>
       </c>
       <c r="O12">
-        <v>2.16488205</v>
+        <v>2.159970255</v>
       </c>
       <c r="P12">
-        <v>7.45681595</v>
+        <v>7.439897545</v>
       </c>
       <c r="Q12">
-        <v>9.616815949999999</v>
+        <v>9.599897545000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2045517518774425</v>
+        <v>0.2059659604202744</v>
       </c>
       <c r="T12">
-        <v>1.106887470446655</v>
+        <v>1.116747958272123</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>45.07517109325613</v>
+        <v>40.97742826659648</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1875977797740442</v>
+        <v>0.1872007328583902</v>
       </c>
       <c r="C13">
-        <v>40.38150624848788</v>
+        <v>40.00662154981804</v>
       </c>
       <c r="D13">
-        <v>34.85550624848788</v>
+        <v>34.91462154981804</v>
       </c>
       <c r="E13">
-        <v>-10.026</v>
+        <v>-9.592000000000001</v>
       </c>
       <c r="F13">
-        <v>4.774000000000001</v>
+        <v>5.208</v>
       </c>
       <c r="G13">
         <v>10.3</v>
@@ -2353,28 +2353,28 @@
         <v>9.84</v>
       </c>
       <c r="M13">
-        <v>0.2401322</v>
+        <v>0.2619624</v>
       </c>
       <c r="N13">
-        <v>9.5998678</v>
+        <v>9.5780376</v>
       </c>
       <c r="O13">
-        <v>2.159970255</v>
+        <v>2.15505846</v>
       </c>
       <c r="P13">
-        <v>7.439897545</v>
+        <v>7.42297914</v>
       </c>
       <c r="Q13">
-        <v>9.599897545000001</v>
+        <v>9.582979139999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2059659604202744</v>
+        <v>0.2074123100663525</v>
       </c>
       <c r="T13">
-        <v>1.116747958272123</v>
+        <v>1.126832548093625</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>40.97742826659648</v>
+        <v>37.56264257771345</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1872007328583902</v>
+        <v>0.1868036859427361</v>
       </c>
       <c r="C14">
-        <v>40.00662154981804</v>
+        <v>39.63193771214302</v>
       </c>
       <c r="D14">
-        <v>34.91462154981804</v>
+        <v>34.97393771214303</v>
       </c>
       <c r="E14">
-        <v>-9.592000000000001</v>
+        <v>-9.157999999999999</v>
       </c>
       <c r="F14">
-        <v>5.208</v>
+        <v>5.642000000000001</v>
       </c>
       <c r="G14">
         <v>10.3</v>
@@ -2435,28 +2435,28 @@
         <v>9.84</v>
       </c>
       <c r="M14">
-        <v>0.2619624</v>
+        <v>0.2837926000000001</v>
       </c>
       <c r="N14">
-        <v>9.5780376</v>
+        <v>9.5562074</v>
       </c>
       <c r="O14">
-        <v>2.15505846</v>
+        <v>2.150146665</v>
       </c>
       <c r="P14">
-        <v>7.42297914</v>
+        <v>7.406060735000001</v>
       </c>
       <c r="Q14">
-        <v>9.582979139999999</v>
+        <v>9.566060735000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2074123100663525</v>
+        <v>0.2088919091295818</v>
       </c>
       <c r="T14">
-        <v>1.126832548093625</v>
+        <v>1.137148967566195</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>37.56264257771345</v>
+        <v>34.67320853327394</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1868036859427361</v>
+        <v>0.1864066390270821</v>
       </c>
       <c r="C15">
-        <v>39.63193771214302</v>
+        <v>39.25745576092829</v>
       </c>
       <c r="D15">
-        <v>34.97393771214303</v>
+        <v>35.03345576092828</v>
       </c>
       <c r="E15">
-        <v>-9.157999999999999</v>
+        <v>-8.724</v>
       </c>
       <c r="F15">
-        <v>5.642000000000001</v>
+        <v>6.076000000000001</v>
       </c>
       <c r="G15">
         <v>10.3</v>
@@ -2517,28 +2517,28 @@
         <v>9.84</v>
       </c>
       <c r="M15">
-        <v>0.2837926000000001</v>
+        <v>0.3056228</v>
       </c>
       <c r="N15">
-        <v>9.5562074</v>
+        <v>9.5343772</v>
       </c>
       <c r="O15">
-        <v>2.150146665</v>
+        <v>2.14523487</v>
       </c>
       <c r="P15">
-        <v>7.406060735000001</v>
+        <v>7.38914233</v>
       </c>
       <c r="Q15">
-        <v>9.566060735000001</v>
+        <v>9.54914233</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2088919091295818</v>
+        <v>0.2104059174733513</v>
       </c>
       <c r="T15">
-        <v>1.137148967566195</v>
+        <v>1.147705303770686</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>34.67320853327394</v>
+        <v>32.19655078089723</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1864066390270821</v>
+        <v>0.1860095921114281</v>
       </c>
       <c r="C16">
-        <v>39.25745576092829</v>
+        <v>38.88317672863158</v>
       </c>
       <c r="D16">
-        <v>35.03345576092828</v>
+        <v>35.09317672863158</v>
       </c>
       <c r="E16">
-        <v>-8.724</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="F16">
-        <v>6.076000000000001</v>
+        <v>6.510000000000002</v>
       </c>
       <c r="G16">
         <v>10.3</v>
@@ -2599,28 +2599,28 @@
         <v>9.84</v>
       </c>
       <c r="M16">
-        <v>0.3056228</v>
+        <v>0.327453</v>
       </c>
       <c r="N16">
-        <v>9.5343772</v>
+        <v>9.512547</v>
       </c>
       <c r="O16">
-        <v>2.14523487</v>
+        <v>2.140323075</v>
       </c>
       <c r="P16">
-        <v>7.38914233</v>
+        <v>7.372223925</v>
       </c>
       <c r="Q16">
-        <v>9.54914233</v>
+        <v>9.532223925</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2104059174733513</v>
+        <v>0.2119555495428566</v>
       </c>
       <c r="T16">
-        <v>1.147705303770686</v>
+        <v>1.158510024356459</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>32.19655078089723</v>
+        <v>30.05011406217075</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1860095921114281</v>
+        <v>0.185612545195774</v>
       </c>
       <c r="C17">
-        <v>38.88317672863159</v>
+        <v>38.5091016547628</v>
       </c>
       <c r="D17">
-        <v>35.09317672863158</v>
+        <v>35.15310165476281</v>
       </c>
       <c r="E17">
-        <v>-8.289999999999999</v>
+        <v>-7.856</v>
       </c>
       <c r="F17">
-        <v>6.510000000000001</v>
+        <v>6.944000000000001</v>
       </c>
       <c r="G17">
         <v>10.3</v>
@@ -2681,28 +2681,28 @@
         <v>9.84</v>
       </c>
       <c r="M17">
-        <v>0.327453</v>
+        <v>0.3492832</v>
       </c>
       <c r="N17">
-        <v>9.512547</v>
+        <v>9.4907168</v>
       </c>
       <c r="O17">
-        <v>2.140323075</v>
+        <v>2.13541128</v>
       </c>
       <c r="P17">
-        <v>7.372223925</v>
+        <v>7.35530552</v>
       </c>
       <c r="Q17">
-        <v>9.532223925</v>
+        <v>9.51530552</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2119555495428566</v>
+        <v>0.2135420776140167</v>
       </c>
       <c r="T17">
-        <v>1.158510024356459</v>
+        <v>1.169572000194274</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>30.05011406217075</v>
+        <v>28.17198193328508</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.185612545195774</v>
+        <v>0.18521549828012</v>
       </c>
       <c r="C18">
-        <v>38.5091016547628</v>
+        <v>38.1352315859442</v>
       </c>
       <c r="D18">
-        <v>35.15310165476281</v>
+        <v>35.2132315859442</v>
       </c>
       <c r="E18">
-        <v>-7.856</v>
+        <v>-7.421999999999999</v>
       </c>
       <c r="F18">
-        <v>6.944000000000001</v>
+        <v>7.378000000000002</v>
       </c>
       <c r="G18">
         <v>10.3</v>
@@ -2763,28 +2763,28 @@
         <v>9.84</v>
       </c>
       <c r="M18">
-        <v>0.3492832</v>
+        <v>0.3711134000000001</v>
       </c>
       <c r="N18">
-        <v>9.4907168</v>
+        <v>9.468886599999999</v>
       </c>
       <c r="O18">
-        <v>2.13541128</v>
+        <v>2.130499485</v>
       </c>
       <c r="P18">
-        <v>7.35530552</v>
+        <v>7.338387115</v>
       </c>
       <c r="Q18">
-        <v>9.51530552</v>
+        <v>9.498387115</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2135420776140167</v>
+        <v>0.215166835277253</v>
       </c>
       <c r="T18">
-        <v>1.169572000194274</v>
+        <v>1.180900529666735</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>28.17198193328508</v>
+        <v>26.51480652544478</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.18521549828012</v>
+        <v>0.184818451364466</v>
       </c>
       <c r="C19">
-        <v>38.1352315859442</v>
+        <v>37.76156757597135</v>
       </c>
       <c r="D19">
-        <v>35.2132315859442</v>
+        <v>35.27356757597136</v>
       </c>
       <c r="E19">
-        <v>-7.421999999999999</v>
+        <v>-6.987999999999999</v>
       </c>
       <c r="F19">
-        <v>7.378000000000002</v>
+        <v>7.812000000000002</v>
       </c>
       <c r="G19">
         <v>10.3</v>
@@ -2845,28 +2845,28 @@
         <v>9.84</v>
       </c>
       <c r="M19">
-        <v>0.3711134000000001</v>
+        <v>0.3929436000000001</v>
       </c>
       <c r="N19">
-        <v>9.468886599999999</v>
+        <v>9.447056399999999</v>
       </c>
       <c r="O19">
-        <v>2.130499485</v>
+        <v>2.12558769</v>
       </c>
       <c r="P19">
-        <v>7.338387115</v>
+        <v>7.32146871</v>
       </c>
       <c r="Q19">
-        <v>9.498387115</v>
+        <v>9.48146871</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.215166835277253</v>
+        <v>0.216831221176178</v>
       </c>
       <c r="T19">
-        <v>1.180900529666735</v>
+        <v>1.192505364736085</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>26.51480652544478</v>
+        <v>25.04176171847562</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.184818451364466</v>
+        <v>0.1844214044488119</v>
       </c>
       <c r="C20">
-        <v>37.76156757597136</v>
+        <v>37.38811068587476</v>
       </c>
       <c r="D20">
-        <v>35.27356757597136</v>
+        <v>35.33411068587476</v>
       </c>
       <c r="E20">
-        <v>-6.988</v>
+        <v>-6.554</v>
       </c>
       <c r="F20">
-        <v>7.812000000000001</v>
+        <v>8.246</v>
       </c>
       <c r="G20">
         <v>10.3</v>
@@ -2927,28 +2927,28 @@
         <v>9.84</v>
       </c>
       <c r="M20">
-        <v>0.3929436000000001</v>
+        <v>0.4147738</v>
       </c>
       <c r="N20">
-        <v>9.447056399999999</v>
+        <v>9.425226199999999</v>
       </c>
       <c r="O20">
-        <v>2.12558769</v>
+        <v>2.120675895</v>
       </c>
       <c r="P20">
-        <v>7.32146871</v>
+        <v>7.304550304999999</v>
       </c>
       <c r="Q20">
-        <v>9.48146871</v>
+        <v>9.464550304999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.216831221176178</v>
+        <v>0.2185367030232246</v>
       </c>
       <c r="T20">
-        <v>1.192505364736085</v>
+        <v>1.20439673894295</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>25.04176171847562</v>
+        <v>23.72377425960849</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1844214044488119</v>
+        <v>0.1840243575331579</v>
       </c>
       <c r="C21">
-        <v>37.38811068587476</v>
+        <v>37.01486198398194</v>
       </c>
       <c r="D21">
-        <v>35.33411068587476</v>
+        <v>35.39486198398193</v>
       </c>
       <c r="E21">
-        <v>-6.554</v>
+        <v>-6.119999999999999</v>
       </c>
       <c r="F21">
-        <v>8.246</v>
+        <v>8.680000000000001</v>
       </c>
       <c r="G21">
         <v>10.3</v>
@@ -3009,28 +3009,28 @@
         <v>9.84</v>
       </c>
       <c r="M21">
-        <v>0.4147738</v>
+        <v>0.436604</v>
       </c>
       <c r="N21">
-        <v>9.425226199999999</v>
+        <v>9.403395999999999</v>
       </c>
       <c r="O21">
-        <v>2.120675895</v>
+        <v>2.1157641</v>
       </c>
       <c r="P21">
-        <v>7.304550304999999</v>
+        <v>7.287631899999999</v>
       </c>
       <c r="Q21">
-        <v>9.464550304999999</v>
+        <v>9.447631899999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2185367030232246</v>
+        <v>0.2202848219164474</v>
       </c>
       <c r="T21">
-        <v>1.20439673894295</v>
+        <v>1.216585397504988</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>23.72377425960849</v>
+        <v>22.53758554662806</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1840243575331579</v>
+        <v>0.1836273106175039</v>
       </c>
       <c r="C22">
-        <v>37.01486198398194</v>
+        <v>36.64182254598038</v>
       </c>
       <c r="D22">
-        <v>35.39486198398193</v>
+        <v>35.45582254598038</v>
       </c>
       <c r="E22">
-        <v>-6.119999999999999</v>
+        <v>-5.685999999999998</v>
       </c>
       <c r="F22">
-        <v>8.680000000000001</v>
+        <v>9.114000000000003</v>
       </c>
       <c r="G22">
         <v>10.3</v>
@@ -3091,28 +3091,28 @@
         <v>9.84</v>
       </c>
       <c r="M22">
-        <v>0.436604</v>
+        <v>0.4584342000000001</v>
       </c>
       <c r="N22">
-        <v>9.403395999999999</v>
+        <v>9.381565800000001</v>
       </c>
       <c r="O22">
-        <v>2.1157641</v>
+        <v>2.110852305</v>
       </c>
       <c r="P22">
-        <v>7.287631899999999</v>
+        <v>7.270713495000001</v>
       </c>
       <c r="Q22">
-        <v>9.447631899999999</v>
+        <v>9.430713495000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2202848219164474</v>
+        <v>0.2220771969841821</v>
       </c>
       <c r="T22">
-        <v>1.216585397504988</v>
+        <v>1.229082629701506</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>22.53758554662806</v>
+        <v>21.46436718726482</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1836273106175039</v>
+        <v>0.1832302637018498</v>
       </c>
       <c r="C23">
-        <v>36.64182254598038</v>
+        <v>36.26899345498097</v>
       </c>
       <c r="D23">
-        <v>35.45582254598038</v>
+        <v>35.51699345498098</v>
       </c>
       <c r="E23">
-        <v>-5.686</v>
+        <v>-5.251999999999999</v>
       </c>
       <c r="F23">
-        <v>9.114000000000001</v>
+        <v>9.548000000000002</v>
       </c>
       <c r="G23">
         <v>10.3</v>
@@ -3173,28 +3173,28 @@
         <v>9.84</v>
       </c>
       <c r="M23">
-        <v>0.4584342</v>
+        <v>0.4802644000000001</v>
       </c>
       <c r="N23">
-        <v>9.381565800000001</v>
+        <v>9.3597356</v>
       </c>
       <c r="O23">
-        <v>2.110852305</v>
+        <v>2.10594051</v>
       </c>
       <c r="P23">
-        <v>7.270713495000001</v>
+        <v>7.253795090000001</v>
       </c>
       <c r="Q23">
-        <v>9.430713495000001</v>
+        <v>9.413795090000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2220771969841821</v>
+        <v>0.2239155303869869</v>
       </c>
       <c r="T23">
-        <v>1.229082629701506</v>
+        <v>1.241900303749218</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.46436718726483</v>
+        <v>20.48871413329824</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1832302637018498</v>
+        <v>0.1828332167861958</v>
       </c>
       <c r="C24">
-        <v>36.26899345498097</v>
+        <v>35.89637580158217</v>
       </c>
       <c r="D24">
-        <v>35.51699345498098</v>
+        <v>35.57837580158217</v>
       </c>
       <c r="E24">
-        <v>-5.251999999999999</v>
+        <v>-4.818</v>
       </c>
       <c r="F24">
-        <v>9.548000000000002</v>
+        <v>9.982000000000001</v>
       </c>
       <c r="G24">
         <v>10.3</v>
@@ -3255,28 +3255,28 @@
         <v>9.84</v>
       </c>
       <c r="M24">
-        <v>0.4802644000000001</v>
+        <v>0.5020946000000001</v>
       </c>
       <c r="N24">
-        <v>9.3597356</v>
+        <v>9.3379054</v>
       </c>
       <c r="O24">
-        <v>2.10594051</v>
+        <v>2.101028715</v>
       </c>
       <c r="P24">
-        <v>7.253795090000001</v>
+        <v>7.236876685</v>
       </c>
       <c r="Q24">
-        <v>9.413795090000001</v>
+        <v>9.396876685000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2239155303869869</v>
+        <v>0.2258016127093452</v>
       </c>
       <c r="T24">
-        <v>1.241900303749218</v>
+        <v>1.255050904395571</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.48871413329824</v>
+        <v>19.59790047532875</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1828332167861958</v>
+        <v>0.1824361698705418</v>
       </c>
       <c r="C25">
-        <v>35.89637580158217</v>
+        <v>35.52397068393476</v>
       </c>
       <c r="D25">
-        <v>35.57837580158217</v>
+        <v>35.63997068393476</v>
       </c>
       <c r="E25">
-        <v>-4.818</v>
+        <v>-4.383999999999999</v>
       </c>
       <c r="F25">
-        <v>9.982000000000001</v>
+        <v>10.416</v>
       </c>
       <c r="G25">
         <v>10.3</v>
@@ -3337,28 +3337,28 @@
         <v>9.84</v>
       </c>
       <c r="M25">
-        <v>0.5020946000000001</v>
+        <v>0.5239248000000001</v>
       </c>
       <c r="N25">
-        <v>9.3379054</v>
+        <v>9.3160752</v>
       </c>
       <c r="O25">
-        <v>2.101028715</v>
+        <v>2.09611692</v>
       </c>
       <c r="P25">
-        <v>7.236876685</v>
+        <v>7.21995828</v>
       </c>
       <c r="Q25">
-        <v>9.396876685000001</v>
+        <v>9.37995828</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2258016127093452</v>
+        <v>0.2277373287770286</v>
       </c>
       <c r="T25">
-        <v>1.255050904395571</v>
+        <v>1.268547573479987</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>19.59790047532875</v>
+        <v>18.78132128885672</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1824361698705418</v>
+        <v>0.1820391229548877</v>
       </c>
       <c r="C26">
-        <v>35.52397068393476</v>
+        <v>35.15177920780744</v>
       </c>
       <c r="D26">
-        <v>35.63997068393476</v>
+        <v>35.70177920780744</v>
       </c>
       <c r="E26">
-        <v>-4.384</v>
+        <v>-3.949999999999999</v>
       </c>
       <c r="F26">
-        <v>10.416</v>
+        <v>10.85</v>
       </c>
       <c r="G26">
         <v>10.3</v>
@@ -3419,28 +3419,28 @@
         <v>9.84</v>
       </c>
       <c r="M26">
-        <v>0.5239248</v>
+        <v>0.545755</v>
       </c>
       <c r="N26">
-        <v>9.3160752</v>
+        <v>9.294245</v>
       </c>
       <c r="O26">
-        <v>2.09611692</v>
+        <v>2.091205125</v>
       </c>
       <c r="P26">
-        <v>7.21995828</v>
+        <v>7.203039875</v>
       </c>
       <c r="Q26">
-        <v>9.37995828</v>
+        <v>9.363039875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2277373287770286</v>
+        <v>0.2297246639398503</v>
       </c>
       <c r="T26">
-        <v>1.268547573479987</v>
+        <v>1.282404153739987</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>18.78132128885672</v>
+        <v>18.03006843730245</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1820391229548877</v>
+        <v>0.1816420760392337</v>
       </c>
       <c r="C27">
-        <v>35.15177920780744</v>
+        <v>34.77980248665291</v>
       </c>
       <c r="D27">
-        <v>35.70177920780744</v>
+        <v>35.76380248665291</v>
       </c>
       <c r="E27">
-        <v>-3.949999999999999</v>
+        <v>-3.515999999999998</v>
       </c>
       <c r="F27">
-        <v>10.85</v>
+        <v>11.284</v>
       </c>
       <c r="G27">
         <v>10.3</v>
@@ -3501,28 +3501,28 @@
         <v>9.84</v>
       </c>
       <c r="M27">
-        <v>0.545755</v>
+        <v>0.5675852000000001</v>
       </c>
       <c r="N27">
-        <v>9.294245</v>
+        <v>9.2724148</v>
       </c>
       <c r="O27">
-        <v>2.091205125</v>
+        <v>2.08629333</v>
       </c>
       <c r="P27">
-        <v>7.203039875</v>
+        <v>7.18612147</v>
       </c>
       <c r="Q27">
-        <v>9.363039875</v>
+        <v>9.34612147</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2297246639398503</v>
+        <v>0.2317657108638293</v>
       </c>
       <c r="T27">
-        <v>1.282404153739987</v>
+        <v>1.296635236169176</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.03006843730245</v>
+        <v>17.33660426663697</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1816420760392337</v>
+        <v>0.1812450291235796</v>
       </c>
       <c r="C28">
-        <v>34.77980248665291</v>
+        <v>34.40804164167479</v>
       </c>
       <c r="D28">
-        <v>35.76380248665291</v>
+        <v>35.82604164167478</v>
       </c>
       <c r="E28">
-        <v>-3.515999999999998</v>
+        <v>-3.081999999999999</v>
       </c>
       <c r="F28">
-        <v>11.284</v>
+        <v>11.718</v>
       </c>
       <c r="G28">
         <v>10.3</v>
@@ -3583,28 +3583,28 @@
         <v>9.84</v>
       </c>
       <c r="M28">
-        <v>0.5675852000000001</v>
+        <v>0.5894154</v>
       </c>
       <c r="N28">
-        <v>9.2724148</v>
+        <v>9.2505846</v>
       </c>
       <c r="O28">
-        <v>2.08629333</v>
+        <v>2.081381535</v>
       </c>
       <c r="P28">
-        <v>7.18612147</v>
+        <v>7.169203065</v>
       </c>
       <c r="Q28">
-        <v>9.34612147</v>
+        <v>9.329203065</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2317657108638293</v>
+        <v>0.2338626768816159</v>
       </c>
       <c r="T28">
-        <v>1.296635236169176</v>
+        <v>1.311256211267658</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.33660426663697</v>
+        <v>16.69450781231708</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1812450291235796</v>
+        <v>0.1808479822079256</v>
       </c>
       <c r="C29">
-        <v>34.40804164167479</v>
+        <v>34.03649780189508</v>
       </c>
       <c r="D29">
-        <v>35.82604164167478</v>
+        <v>35.88849780189508</v>
       </c>
       <c r="E29">
-        <v>-3.081999999999999</v>
+        <v>-2.647999999999998</v>
       </c>
       <c r="F29">
-        <v>11.718</v>
+        <v>12.152</v>
       </c>
       <c r="G29">
         <v>10.3</v>
@@ -3665,28 +3665,28 @@
         <v>9.84</v>
       </c>
       <c r="M29">
-        <v>0.5894154</v>
+        <v>0.6112456000000001</v>
       </c>
       <c r="N29">
-        <v>9.2505846</v>
+        <v>9.2287544</v>
       </c>
       <c r="O29">
-        <v>2.081381535</v>
+        <v>2.07646974</v>
       </c>
       <c r="P29">
-        <v>7.169203065</v>
+        <v>7.152284659999999</v>
       </c>
       <c r="Q29">
-        <v>9.329203065</v>
+        <v>9.31228466</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2338626768816159</v>
+        <v>0.2360178919554522</v>
       </c>
       <c r="T29">
-        <v>1.311256211267658</v>
+        <v>1.32628332456332</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.69450781231708</v>
+        <v>16.09827539044862</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1808479822079256</v>
+        <v>0.1804509352922716</v>
       </c>
       <c r="C30">
-        <v>34.03649780189508</v>
+        <v>33.66517210422261</v>
       </c>
       <c r="D30">
-        <v>35.88849780189508</v>
+        <v>35.95117210422262</v>
       </c>
       <c r="E30">
-        <v>-2.647999999999998</v>
+        <v>-2.213999999999997</v>
       </c>
       <c r="F30">
-        <v>12.152</v>
+        <v>12.586</v>
       </c>
       <c r="G30">
         <v>10.3</v>
@@ -3747,28 +3747,28 @@
         <v>9.84</v>
       </c>
       <c r="M30">
-        <v>0.6112456000000001</v>
+        <v>0.6330758000000002</v>
       </c>
       <c r="N30">
-        <v>9.2287544</v>
+        <v>9.2069242</v>
       </c>
       <c r="O30">
-        <v>2.07646974</v>
+        <v>2.071557945</v>
       </c>
       <c r="P30">
-        <v>7.152284659999999</v>
+        <v>7.135366254999999</v>
       </c>
       <c r="Q30">
-        <v>9.31228466</v>
+        <v>9.295366254999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2360178919554522</v>
+        <v>0.2382338173130586</v>
       </c>
       <c r="T30">
-        <v>1.32628332456332</v>
+        <v>1.341733736825057</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.09827539044862</v>
+        <v>15.54316244595038</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1804509352922715</v>
+        <v>0.1800538883766175</v>
       </c>
       <c r="C31">
-        <v>33.66517210422263</v>
+        <v>33.29406569352187</v>
       </c>
       <c r="D31">
-        <v>35.95117210422263</v>
+        <v>36.01406569352187</v>
       </c>
       <c r="E31">
-        <v>-2.214</v>
+        <v>-1.779999999999999</v>
       </c>
       <c r="F31">
-        <v>12.586</v>
+        <v>13.02</v>
       </c>
       <c r="G31">
         <v>10.3</v>
@@ -3829,28 +3829,28 @@
         <v>9.84</v>
       </c>
       <c r="M31">
-        <v>0.6330758</v>
+        <v>0.654906</v>
       </c>
       <c r="N31">
-        <v>9.2069242</v>
+        <v>9.185093999999999</v>
       </c>
       <c r="O31">
-        <v>2.071557945</v>
+        <v>2.06664615</v>
       </c>
       <c r="P31">
-        <v>7.135366254999999</v>
+        <v>7.118447849999999</v>
       </c>
       <c r="Q31">
-        <v>9.295366254999999</v>
+        <v>9.278447849999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2382338173130585</v>
+        <v>0.2405130548237393</v>
       </c>
       <c r="T31">
-        <v>1.341733736825057</v>
+        <v>1.357625589437129</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.54316244595039</v>
+        <v>15.02505703108538</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1800538883766175</v>
+        <v>0.1796568414609634</v>
       </c>
       <c r="C32">
-        <v>33.29406569352187</v>
+        <v>32.92317972268277</v>
       </c>
       <c r="D32">
-        <v>36.01406569352187</v>
+        <v>36.07717972268276</v>
       </c>
       <c r="E32">
-        <v>-1.779999999999999</v>
+        <v>-1.345999999999998</v>
       </c>
       <c r="F32">
-        <v>13.02</v>
+        <v>13.454</v>
       </c>
       <c r="G32">
         <v>10.3</v>
@@ -3911,28 +3911,28 @@
         <v>9.84</v>
       </c>
       <c r="M32">
-        <v>0.654906</v>
+        <v>0.6767362000000001</v>
       </c>
       <c r="N32">
-        <v>9.185093999999999</v>
+        <v>9.163263799999999</v>
       </c>
       <c r="O32">
-        <v>2.06664615</v>
+        <v>2.061734355</v>
       </c>
       <c r="P32">
-        <v>7.118447849999999</v>
+        <v>7.101529444999999</v>
       </c>
       <c r="Q32">
-        <v>9.278447849999999</v>
+        <v>9.261529444999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2405130548237393</v>
+        <v>0.2428583571898021</v>
       </c>
       <c r="T32">
-        <v>1.357625589437129</v>
+        <v>1.373978075458247</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.02505703108538</v>
+        <v>14.5403777720181</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1796568414609634</v>
+        <v>0.1792597945453094</v>
       </c>
       <c r="C33">
-        <v>32.92317972268277</v>
+        <v>32.55251535269105</v>
       </c>
       <c r="D33">
-        <v>36.07717972268276</v>
+        <v>36.14051535269105</v>
       </c>
       <c r="E33">
-        <v>-1.345999999999998</v>
+        <v>-0.911999999999999</v>
       </c>
       <c r="F33">
-        <v>13.454</v>
+        <v>13.888</v>
       </c>
       <c r="G33">
         <v>10.3</v>
@@ -3993,28 +3993,28 @@
         <v>9.84</v>
       </c>
       <c r="M33">
-        <v>0.6767362000000001</v>
+        <v>0.6985664</v>
       </c>
       <c r="N33">
-        <v>9.163263799999999</v>
+        <v>9.141433599999999</v>
       </c>
       <c r="O33">
-        <v>2.061734355</v>
+        <v>2.05682256</v>
       </c>
       <c r="P33">
-        <v>7.101529444999999</v>
+        <v>7.084611039999999</v>
       </c>
       <c r="Q33">
-        <v>9.261529444999999</v>
+        <v>9.244611039999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2428583571898021</v>
+        <v>0.2452726390372198</v>
       </c>
       <c r="T33">
-        <v>1.373978075458247</v>
+        <v>1.390811516950574</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.5403777720181</v>
+        <v>14.08599096664254</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1792597945453094</v>
+        <v>0.1788627476296554</v>
       </c>
       <c r="C34">
-        <v>32.55251535269105</v>
+        <v>32.18207375269957</v>
       </c>
       <c r="D34">
-        <v>36.14051535269105</v>
+        <v>36.20407375269956</v>
       </c>
       <c r="E34">
-        <v>-0.911999999999999</v>
+        <v>-0.477999999999998</v>
       </c>
       <c r="F34">
-        <v>13.888</v>
+        <v>14.322</v>
       </c>
       <c r="G34">
         <v>10.3</v>
@@ -4075,28 +4075,28 @@
         <v>9.84</v>
       </c>
       <c r="M34">
-        <v>0.6985664</v>
+        <v>0.7203966000000001</v>
       </c>
       <c r="N34">
-        <v>9.141433599999999</v>
+        <v>9.119603399999999</v>
       </c>
       <c r="O34">
-        <v>2.05682256</v>
+        <v>2.051910765</v>
       </c>
       <c r="P34">
-        <v>7.084611039999999</v>
+        <v>7.067692634999999</v>
       </c>
       <c r="Q34">
-        <v>9.244611039999999</v>
+        <v>9.227692635</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2452726390372198</v>
+        <v>0.2477589889994857</v>
       </c>
       <c r="T34">
-        <v>1.390811516950574</v>
+        <v>1.408147449233717</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.08599096664254</v>
+        <v>13.65914275553216</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1788627476296554</v>
+        <v>0.1784657007140013</v>
       </c>
       <c r="C35">
-        <v>32.18207375269957</v>
+        <v>31.81185610010017</v>
       </c>
       <c r="D35">
-        <v>36.20407375269956</v>
+        <v>36.26785610010017</v>
       </c>
       <c r="E35">
-        <v>-0.477999999999998</v>
+        <v>-0.04399999999999693</v>
       </c>
       <c r="F35">
-        <v>14.322</v>
+        <v>14.756</v>
       </c>
       <c r="G35">
         <v>10.3</v>
@@ -4157,28 +4157,28 @@
         <v>9.84</v>
       </c>
       <c r="M35">
-        <v>0.7203966000000001</v>
+        <v>0.7422268000000002</v>
       </c>
       <c r="N35">
-        <v>9.119603399999999</v>
+        <v>9.097773199999999</v>
       </c>
       <c r="O35">
-        <v>2.051910765</v>
+        <v>2.04699897</v>
       </c>
       <c r="P35">
-        <v>7.067692634999999</v>
+        <v>7.050774229999999</v>
       </c>
       <c r="Q35">
-        <v>9.227692635</v>
+        <v>9.210774229999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2477589889994857</v>
+        <v>0.2503206829000021</v>
       </c>
       <c r="T35">
-        <v>1.408147449233717</v>
+        <v>1.426008712798167</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.65914275553216</v>
+        <v>13.25740326272239</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1784657007140013</v>
+        <v>0.1780686537983473</v>
       </c>
       <c r="C36">
-        <v>31.81185610010017</v>
+        <v>31.44186358059635</v>
       </c>
       <c r="D36">
-        <v>36.26785610010017</v>
+        <v>36.33186358059636</v>
       </c>
       <c r="E36">
-        <v>-0.04399999999999693</v>
+        <v>0.3900000000000023</v>
       </c>
       <c r="F36">
-        <v>14.756</v>
+        <v>15.19</v>
       </c>
       <c r="G36">
         <v>10.3</v>
@@ -4239,28 +4239,28 @@
         <v>9.84</v>
       </c>
       <c r="M36">
-        <v>0.7422268000000002</v>
+        <v>0.7640570000000001</v>
       </c>
       <c r="N36">
-        <v>9.097773199999999</v>
+        <v>9.075943000000001</v>
       </c>
       <c r="O36">
-        <v>2.04699897</v>
+        <v>2.042087175</v>
       </c>
       <c r="P36">
-        <v>7.050774229999999</v>
+        <v>7.033855825</v>
       </c>
       <c r="Q36">
-        <v>9.210774229999998</v>
+        <v>9.193855825</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2503206829000021</v>
+        <v>0.2529611981513036</v>
       </c>
       <c r="T36">
-        <v>1.426008712798167</v>
+        <v>1.444419553703062</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.25740326272239</v>
+        <v>12.87862031235889</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1780686537983473</v>
+        <v>0.1780901068826933</v>
       </c>
       <c r="C37">
-        <v>31.44186358059635</v>
+        <v>31.00439938005203</v>
       </c>
       <c r="D37">
-        <v>36.33186358059636</v>
+        <v>36.32839938005203</v>
       </c>
       <c r="E37">
-        <v>0.3900000000000023</v>
+        <v>0.8240000000000034</v>
       </c>
       <c r="F37">
-        <v>15.19</v>
+        <v>15.624</v>
       </c>
       <c r="G37">
         <v>10.3</v>
@@ -4321,45 +4321,45 @@
         <v>9.84</v>
       </c>
       <c r="M37">
-        <v>0.7640570000000001</v>
+        <v>0.8093232000000002</v>
       </c>
       <c r="N37">
-        <v>9.075943000000001</v>
+        <v>9.0306768</v>
       </c>
       <c r="O37">
-        <v>2.042087175</v>
+        <v>2.03190228</v>
       </c>
       <c r="P37">
-        <v>7.033855825</v>
+        <v>6.99877452</v>
       </c>
       <c r="Q37">
-        <v>9.193855825</v>
+        <v>9.15877452</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2529611981513036</v>
+        <v>0.2556842295042083</v>
       </c>
       <c r="T37">
-        <v>1.444419553703062</v>
+        <v>1.463405733386235</v>
       </c>
       <c r="U37">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V37">
         <v>0.225</v>
       </c>
       <c r="W37">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y37">
-        <v>12.87862031235889</v>
+        <v>12.15830708918266</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1780901068826933</v>
+        <v>0.1777046849670393</v>
       </c>
       <c r="C38">
-        <v>31.00439938005201</v>
+        <v>30.63273738109521</v>
       </c>
       <c r="D38">
-        <v>36.32839938005202</v>
+        <v>36.39073738109521</v>
       </c>
       <c r="E38">
-        <v>0.8240000000000016</v>
+        <v>1.258000000000003</v>
       </c>
       <c r="F38">
-        <v>15.624</v>
+        <v>16.058</v>
       </c>
       <c r="G38">
         <v>10.3</v>
@@ -4403,28 +4403,28 @@
         <v>9.84</v>
       </c>
       <c r="M38">
-        <v>0.8093232000000001</v>
+        <v>0.8318044000000001</v>
       </c>
       <c r="N38">
-        <v>9.0306768</v>
+        <v>9.008195600000001</v>
       </c>
       <c r="O38">
-        <v>2.03190228</v>
+        <v>2.02684401</v>
       </c>
       <c r="P38">
-        <v>6.99877452</v>
+        <v>6.981351590000001</v>
       </c>
       <c r="Q38">
-        <v>9.15877452</v>
+        <v>9.141351590000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2556842295042083</v>
+        <v>0.2584937062968877</v>
       </c>
       <c r="T38">
-        <v>1.463405733386235</v>
+        <v>1.482994648932366</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.15830708918266</v>
+        <v>11.82970419488043</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1777046849670393</v>
+        <v>0.1773192630513852</v>
       </c>
       <c r="C39">
-        <v>30.63273738109521</v>
+        <v>30.26128968864019</v>
       </c>
       <c r="D39">
-        <v>36.39073738109521</v>
+        <v>36.45328968864019</v>
       </c>
       <c r="E39">
-        <v>1.258000000000003</v>
+        <v>1.692</v>
       </c>
       <c r="F39">
-        <v>16.058</v>
+        <v>16.492</v>
       </c>
       <c r="G39">
         <v>10.3</v>
@@ -4485,28 +4485,28 @@
         <v>9.84</v>
       </c>
       <c r="M39">
-        <v>0.8318044000000001</v>
+        <v>0.8542856</v>
       </c>
       <c r="N39">
-        <v>9.008195600000001</v>
+        <v>8.985714399999999</v>
       </c>
       <c r="O39">
-        <v>2.02684401</v>
+        <v>2.02178574</v>
       </c>
       <c r="P39">
-        <v>6.981351590000001</v>
+        <v>6.963928659999999</v>
       </c>
       <c r="Q39">
-        <v>9.141351590000001</v>
+        <v>9.123928659999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2584937062968877</v>
+        <v>0.261393811373202</v>
       </c>
       <c r="T39">
-        <v>1.482994648932366</v>
+        <v>1.503215464979985</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.82970419488043</v>
+        <v>11.518396189752</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1773192630513852</v>
+        <v>0.1769338411357312</v>
       </c>
       <c r="C40">
-        <v>30.26128968864019</v>
+        <v>29.89005740970893</v>
       </c>
       <c r="D40">
-        <v>36.45328968864019</v>
+        <v>36.51605740970894</v>
       </c>
       <c r="E40">
-        <v>1.692</v>
+        <v>2.126000000000001</v>
       </c>
       <c r="F40">
-        <v>16.492</v>
+        <v>16.926</v>
       </c>
       <c r="G40">
         <v>10.3</v>
@@ -4567,28 +4567,28 @@
         <v>9.84</v>
       </c>
       <c r="M40">
-        <v>0.8542856</v>
+        <v>0.8767668000000001</v>
       </c>
       <c r="N40">
-        <v>8.985714399999999</v>
+        <v>8.963233199999999</v>
       </c>
       <c r="O40">
-        <v>2.02178574</v>
+        <v>2.01672747</v>
       </c>
       <c r="P40">
-        <v>6.963928659999999</v>
+        <v>6.94650573</v>
       </c>
       <c r="Q40">
-        <v>9.123928659999999</v>
+        <v>9.10650573</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.261393811373202</v>
+        <v>0.2643890018618544</v>
       </c>
       <c r="T40">
-        <v>1.503215464979985</v>
+        <v>1.524099258602935</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.518396189752</v>
+        <v>11.22305269770707</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1769338411357312</v>
+        <v>0.1765484192200771</v>
       </c>
       <c r="C41">
-        <v>29.89005740970893</v>
+        <v>29.51904165896113</v>
       </c>
       <c r="D41">
-        <v>36.51605740970894</v>
+        <v>36.57904165896112</v>
       </c>
       <c r="E41">
-        <v>2.126000000000001</v>
+        <v>2.560000000000002</v>
       </c>
       <c r="F41">
-        <v>16.926</v>
+        <v>17.36</v>
       </c>
       <c r="G41">
         <v>10.3</v>
@@ -4649,28 +4649,28 @@
         <v>9.84</v>
       </c>
       <c r="M41">
-        <v>0.8767668000000001</v>
+        <v>0.8992480000000002</v>
       </c>
       <c r="N41">
-        <v>8.963233199999999</v>
+        <v>8.940752</v>
       </c>
       <c r="O41">
-        <v>2.01672747</v>
+        <v>2.0116692</v>
       </c>
       <c r="P41">
-        <v>6.94650573</v>
+        <v>6.9290828</v>
       </c>
       <c r="Q41">
-        <v>9.10650573</v>
+        <v>9.0890828</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2643890018618544</v>
+        <v>0.2674840320334619</v>
       </c>
       <c r="T41">
-        <v>1.524099258602935</v>
+        <v>1.545679178679984</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.22305269770707</v>
+        <v>10.9424763802644</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1765484192200771</v>
+        <v>0.1761629973044231</v>
       </c>
       <c r="C42">
-        <v>29.51904165896113</v>
+        <v>29.14824355876014</v>
       </c>
       <c r="D42">
-        <v>36.57904165896112</v>
+        <v>36.64224355876014</v>
       </c>
       <c r="E42">
-        <v>2.560000000000002</v>
+        <v>2.994000000000003</v>
       </c>
       <c r="F42">
-        <v>17.36</v>
+        <v>17.794</v>
       </c>
       <c r="G42">
         <v>10.3</v>
@@ -4731,28 +4731,28 @@
         <v>9.84</v>
       </c>
       <c r="M42">
-        <v>0.8992480000000002</v>
+        <v>0.9217292000000001</v>
       </c>
       <c r="N42">
-        <v>8.940752</v>
+        <v>8.9182708</v>
       </c>
       <c r="O42">
-        <v>2.0116692</v>
+        <v>2.00661093</v>
       </c>
       <c r="P42">
-        <v>6.9290828</v>
+        <v>6.91165987</v>
       </c>
       <c r="Q42">
-        <v>9.0890828</v>
+        <v>9.071659870000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2674840320334619</v>
+        <v>0.2706839784820731</v>
       </c>
       <c r="T42">
-        <v>1.545679178679984</v>
+        <v>1.567990621471509</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.9424763802644</v>
+        <v>10.67558671245307</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1761629973044231</v>
+        <v>0.1757775753887691</v>
       </c>
       <c r="C43">
-        <v>29.14824355876014</v>
+        <v>28.77766423923982</v>
       </c>
       <c r="D43">
-        <v>36.64224355876014</v>
+        <v>36.70566423923982</v>
       </c>
       <c r="E43">
-        <v>2.994000000000003</v>
+        <v>3.428000000000004</v>
       </c>
       <c r="F43">
-        <v>17.794</v>
+        <v>18.22800000000001</v>
       </c>
       <c r="G43">
         <v>10.3</v>
@@ -4813,28 +4813,28 @@
         <v>9.84</v>
       </c>
       <c r="M43">
-        <v>0.9217292000000001</v>
+        <v>0.9442104000000002</v>
       </c>
       <c r="N43">
-        <v>8.9182708</v>
+        <v>8.895789600000001</v>
       </c>
       <c r="O43">
-        <v>2.00661093</v>
+        <v>2.00155266</v>
       </c>
       <c r="P43">
-        <v>6.91165987</v>
+        <v>6.894236940000001</v>
       </c>
       <c r="Q43">
-        <v>9.071659870000001</v>
+        <v>9.054236940000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2706839784820731</v>
+        <v>0.2739942679116708</v>
       </c>
       <c r="T43">
-        <v>1.567990621471509</v>
+        <v>1.591071424359294</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.67558671245307</v>
+        <v>10.42140607644228</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1757775753887691</v>
+        <v>0.1753921534731151</v>
       </c>
       <c r="C44">
-        <v>28.77766423923982</v>
+        <v>28.40730483837163</v>
       </c>
       <c r="D44">
-        <v>36.70566423923982</v>
+        <v>36.76930483837164</v>
       </c>
       <c r="E44">
-        <v>3.428000000000001</v>
+        <v>3.862000000000002</v>
       </c>
       <c r="F44">
-        <v>18.228</v>
+        <v>18.662</v>
       </c>
       <c r="G44">
         <v>10.3</v>
@@ -4895,28 +4895,28 @@
         <v>9.84</v>
       </c>
       <c r="M44">
-        <v>0.9442104</v>
+        <v>0.9666916000000001</v>
       </c>
       <c r="N44">
-        <v>8.895789600000001</v>
+        <v>8.873308399999999</v>
       </c>
       <c r="O44">
-        <v>2.00155266</v>
+        <v>1.99649439</v>
       </c>
       <c r="P44">
-        <v>6.894236940000001</v>
+        <v>6.876814009999999</v>
       </c>
       <c r="Q44">
-        <v>9.054236940000001</v>
+        <v>9.036814010000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2739942679116708</v>
+        <v>0.2774207078475703</v>
       </c>
       <c r="T44">
-        <v>1.591071424359294</v>
+        <v>1.614962079979984</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.42140607644228</v>
+        <v>10.17904779559479</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1753921534731151</v>
+        <v>0.175006731557461</v>
       </c>
       <c r="C45">
-        <v>28.40730483837163</v>
+        <v>28.03716650203297</v>
       </c>
       <c r="D45">
-        <v>36.76930483837164</v>
+        <v>36.83316650203297</v>
       </c>
       <c r="E45">
-        <v>3.862000000000002</v>
+        <v>4.296000000000003</v>
       </c>
       <c r="F45">
-        <v>18.662</v>
+        <v>19.096</v>
       </c>
       <c r="G45">
         <v>10.3</v>
@@ -4977,28 +4977,28 @@
         <v>9.84</v>
       </c>
       <c r="M45">
-        <v>0.9666916000000001</v>
+        <v>0.9891728000000002</v>
       </c>
       <c r="N45">
-        <v>8.873308399999999</v>
+        <v>8.850827199999999</v>
       </c>
       <c r="O45">
-        <v>1.99649439</v>
+        <v>1.99143612</v>
       </c>
       <c r="P45">
-        <v>6.876814009999999</v>
+        <v>6.85939108</v>
       </c>
       <c r="Q45">
-        <v>9.036814010000001</v>
+        <v>9.01939108</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2774207078475703</v>
+        <v>0.2809695206383232</v>
       </c>
       <c r="T45">
-        <v>1.614962079979984</v>
+        <v>1.639705973301412</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.17904779559479</v>
+        <v>9.94770580024036</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.175006731557461</v>
+        <v>0.175214184641807</v>
       </c>
       <c r="C46">
-        <v>28.03716650203297</v>
+        <v>27.56876546390277</v>
       </c>
       <c r="D46">
-        <v>36.83316650203297</v>
+        <v>36.79876546390278</v>
       </c>
       <c r="E46">
-        <v>4.296000000000003</v>
+        <v>4.730000000000004</v>
       </c>
       <c r="F46">
-        <v>19.096</v>
+        <v>19.53</v>
       </c>
       <c r="G46">
         <v>10.3</v>
@@ -5059,45 +5059,45 @@
         <v>9.84</v>
       </c>
       <c r="M46">
-        <v>0.9891728000000002</v>
+        <v>1.044855</v>
       </c>
       <c r="N46">
-        <v>8.850827199999999</v>
+        <v>8.795145</v>
       </c>
       <c r="O46">
-        <v>1.99143612</v>
+        <v>1.978907625</v>
       </c>
       <c r="P46">
-        <v>6.85939108</v>
+        <v>6.816237375</v>
       </c>
       <c r="Q46">
-        <v>9.01939108</v>
+        <v>8.976237375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2809695206383232</v>
+        <v>0.2846473811669217</v>
       </c>
       <c r="T46">
-        <v>1.639705973301412</v>
+        <v>1.665349644561801</v>
       </c>
       <c r="U46">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V46">
         <v>0.225</v>
       </c>
       <c r="W46">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>9.94770580024036</v>
+        <v>9.417574687396813</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.175214184641807</v>
+        <v>0.1748419377261529</v>
       </c>
       <c r="C47">
-        <v>27.56876546390277</v>
+        <v>27.19653941651272</v>
       </c>
       <c r="D47">
-        <v>36.79876546390278</v>
+        <v>36.86053941651272</v>
       </c>
       <c r="E47">
-        <v>4.730000000000004</v>
+        <v>5.164000000000001</v>
       </c>
       <c r="F47">
-        <v>19.53</v>
+        <v>19.964</v>
       </c>
       <c r="G47">
         <v>10.3</v>
@@ -5141,28 +5141,28 @@
         <v>9.84</v>
       </c>
       <c r="M47">
-        <v>1.044855</v>
+        <v>1.068074</v>
       </c>
       <c r="N47">
-        <v>8.795145</v>
+        <v>8.771926000000001</v>
       </c>
       <c r="O47">
-        <v>1.978907625</v>
+        <v>1.97368335</v>
       </c>
       <c r="P47">
-        <v>6.816237375</v>
+        <v>6.798242650000001</v>
       </c>
       <c r="Q47">
-        <v>8.976237375</v>
+        <v>8.958242650000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2846473811669217</v>
+        <v>0.288461458752135</v>
       </c>
       <c r="T47">
-        <v>1.665349644561801</v>
+        <v>1.691943081424427</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>9.417574687396813</v>
+        <v>9.212844802888188</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1748419377261529</v>
+        <v>0.1744696908104989</v>
       </c>
       <c r="C48">
-        <v>27.19653941651272</v>
+        <v>26.82452111728407</v>
       </c>
       <c r="D48">
-        <v>36.86053941651272</v>
+        <v>36.92252111728408</v>
       </c>
       <c r="E48">
-        <v>5.164000000000001</v>
+        <v>5.598000000000003</v>
       </c>
       <c r="F48">
-        <v>19.964</v>
+        <v>20.398</v>
       </c>
       <c r="G48">
         <v>10.3</v>
@@ -5223,28 +5223,28 @@
         <v>9.84</v>
       </c>
       <c r="M48">
-        <v>1.068074</v>
+        <v>1.091293</v>
       </c>
       <c r="N48">
-        <v>8.771926000000001</v>
+        <v>8.748707</v>
       </c>
       <c r="O48">
-        <v>1.97368335</v>
+        <v>1.968459075</v>
       </c>
       <c r="P48">
-        <v>6.798242650000001</v>
+        <v>6.780247924999999</v>
       </c>
       <c r="Q48">
-        <v>8.958242650000001</v>
+        <v>8.940247925</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.288461458752135</v>
+        <v>0.2924194637933941</v>
       </c>
       <c r="T48">
-        <v>1.691943081424427</v>
+        <v>1.719540044206397</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.212844802888188</v>
+        <v>9.016826828358653</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1744696908104989</v>
+        <v>0.1740974438948449</v>
       </c>
       <c r="C49">
-        <v>26.82452111728407</v>
+        <v>26.45271161597954</v>
       </c>
       <c r="D49">
-        <v>36.92252111728408</v>
+        <v>36.98471161597954</v>
       </c>
       <c r="E49">
-        <v>5.598000000000003</v>
+        <v>6.032000000000004</v>
       </c>
       <c r="F49">
-        <v>20.398</v>
+        <v>20.832</v>
       </c>
       <c r="G49">
         <v>10.3</v>
@@ -5305,28 +5305,28 @@
         <v>9.84</v>
       </c>
       <c r="M49">
-        <v>1.091293</v>
+        <v>1.114512</v>
       </c>
       <c r="N49">
-        <v>8.748707</v>
+        <v>8.725488</v>
       </c>
       <c r="O49">
-        <v>1.968459075</v>
+        <v>1.9632348</v>
       </c>
       <c r="P49">
-        <v>6.780247924999999</v>
+        <v>6.7622532</v>
       </c>
       <c r="Q49">
-        <v>8.940247925</v>
+        <v>8.9222532</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2924194637933941</v>
+        <v>0.2965296997977786</v>
       </c>
       <c r="T49">
-        <v>1.719540044206397</v>
+        <v>1.748198428633828</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>9.016826828358653</v>
+        <v>8.828976269434513</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1740974438948449</v>
+        <v>0.1737251969791908</v>
       </c>
       <c r="C50">
-        <v>26.45271161597955</v>
+        <v>26.08111196944641</v>
       </c>
       <c r="D50">
-        <v>36.98471161597954</v>
+        <v>37.04711196944642</v>
       </c>
       <c r="E50">
-        <v>6.032</v>
+        <v>6.466000000000001</v>
       </c>
       <c r="F50">
-        <v>20.832</v>
+        <v>21.266</v>
       </c>
       <c r="G50">
         <v>10.3</v>
@@ -5387,28 +5387,28 @@
         <v>9.84</v>
       </c>
       <c r="M50">
-        <v>1.114512</v>
+        <v>1.137731</v>
       </c>
       <c r="N50">
-        <v>8.725488</v>
+        <v>8.702268999999999</v>
       </c>
       <c r="O50">
-        <v>1.9632348</v>
+        <v>1.958010525</v>
       </c>
       <c r="P50">
-        <v>6.7622532</v>
+        <v>6.744258475</v>
       </c>
       <c r="Q50">
-        <v>8.9222532</v>
+        <v>8.904258474999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2965296997977786</v>
+        <v>0.3008011215278251</v>
       </c>
       <c r="T50">
-        <v>1.748198428633828</v>
+        <v>1.777980671274099</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.828976269434516</v>
+        <v>8.648793080262381</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1737251969791908</v>
+        <v>0.1733529500635368</v>
       </c>
       <c r="C51">
-        <v>26.08111196944641</v>
+        <v>25.70972324167647</v>
       </c>
       <c r="D51">
-        <v>37.04711196944642</v>
+        <v>37.10972324167647</v>
       </c>
       <c r="E51">
-        <v>6.466000000000001</v>
+        <v>6.900000000000002</v>
       </c>
       <c r="F51">
-        <v>21.266</v>
+        <v>21.7</v>
       </c>
       <c r="G51">
         <v>10.3</v>
@@ -5469,28 +5469,28 @@
         <v>9.84</v>
       </c>
       <c r="M51">
-        <v>1.137731</v>
+        <v>1.16095</v>
       </c>
       <c r="N51">
-        <v>8.702268999999999</v>
+        <v>8.67905</v>
       </c>
       <c r="O51">
-        <v>1.958010525</v>
+        <v>1.95278625</v>
       </c>
       <c r="P51">
-        <v>6.744258475</v>
+        <v>6.72626375</v>
       </c>
       <c r="Q51">
-        <v>8.904258474999999</v>
+        <v>8.886263750000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3008011215278251</v>
+        <v>0.3052434001270736</v>
       </c>
       <c r="T51">
-        <v>1.777980671274099</v>
+        <v>1.808954203619981</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.648793080262381</v>
+        <v>8.475817218657134</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1733529500635368</v>
+        <v>0.1729807031478828</v>
       </c>
       <c r="C52">
-        <v>25.70972324167647</v>
+        <v>25.33854650386645</v>
       </c>
       <c r="D52">
-        <v>37.10972324167647</v>
+        <v>37.17254650386645</v>
       </c>
       <c r="E52">
-        <v>6.900000000000002</v>
+        <v>7.334000000000003</v>
       </c>
       <c r="F52">
-        <v>21.7</v>
+        <v>22.134</v>
       </c>
       <c r="G52">
         <v>10.3</v>
@@ -5551,28 +5551,28 @@
         <v>9.84</v>
       </c>
       <c r="M52">
-        <v>1.16095</v>
+        <v>1.184169</v>
       </c>
       <c r="N52">
-        <v>8.67905</v>
+        <v>8.655830999999999</v>
       </c>
       <c r="O52">
-        <v>1.95278625</v>
+        <v>1.947561975</v>
       </c>
       <c r="P52">
-        <v>6.72626375</v>
+        <v>6.708269024999999</v>
       </c>
       <c r="Q52">
-        <v>8.886263750000001</v>
+        <v>8.868269025</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3052434001270736</v>
+        <v>0.3098669962201689</v>
       </c>
       <c r="T52">
-        <v>1.808954203619981</v>
+        <v>1.8411919617759</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.475817218657134</v>
+        <v>8.309624724173659</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1729807031478828</v>
+        <v>0.1726084562322287</v>
       </c>
       <c r="C53">
-        <v>25.33854650386645</v>
+        <v>24.96758283447911</v>
       </c>
       <c r="D53">
-        <v>37.17254650386645</v>
+        <v>37.23558283447912</v>
       </c>
       <c r="E53">
-        <v>7.334000000000003</v>
+        <v>7.768000000000004</v>
       </c>
       <c r="F53">
-        <v>22.134</v>
+        <v>22.568</v>
       </c>
       <c r="G53">
         <v>10.3</v>
@@ -5633,28 +5633,28 @@
         <v>9.84</v>
       </c>
       <c r="M53">
-        <v>1.184169</v>
+        <v>1.207388</v>
       </c>
       <c r="N53">
-        <v>8.655830999999999</v>
+        <v>8.632612</v>
       </c>
       <c r="O53">
-        <v>1.947561975</v>
+        <v>1.9423377</v>
       </c>
       <c r="P53">
-        <v>6.708269024999999</v>
+        <v>6.6902743</v>
       </c>
       <c r="Q53">
-        <v>8.868269025</v>
+        <v>8.850274300000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3098669962201689</v>
+        <v>0.3146832421504765</v>
       </c>
       <c r="T53">
-        <v>1.8411919617759</v>
+        <v>1.874772959854981</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.309624724173659</v>
+        <v>8.14982424870878</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1726084562322287</v>
+        <v>0.1722362093165747</v>
       </c>
       <c r="C54">
-        <v>24.96758283447911</v>
+        <v>24.59683331930503</v>
       </c>
       <c r="D54">
-        <v>37.23558283447912</v>
+        <v>37.29883331930503</v>
       </c>
       <c r="E54">
-        <v>7.768000000000004</v>
+        <v>8.202000000000002</v>
       </c>
       <c r="F54">
-        <v>22.568</v>
+        <v>23.002</v>
       </c>
       <c r="G54">
         <v>10.3</v>
@@ -5715,28 +5715,28 @@
         <v>9.84</v>
       </c>
       <c r="M54">
-        <v>1.207388</v>
+        <v>1.230607</v>
       </c>
       <c r="N54">
-        <v>8.632612</v>
+        <v>8.609393000000001</v>
       </c>
       <c r="O54">
-        <v>1.9423377</v>
+        <v>1.937113425</v>
       </c>
       <c r="P54">
-        <v>6.6902743</v>
+        <v>6.672279575000001</v>
       </c>
       <c r="Q54">
-        <v>8.850274300000001</v>
+        <v>8.832279575000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3146832421504765</v>
+        <v>0.3197044347161164</v>
       </c>
       <c r="T54">
-        <v>1.874772959854981</v>
+        <v>1.909782936575725</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.14982424870878</v>
+        <v>7.996053979865222</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1722362093165747</v>
+        <v>0.1718639624009207</v>
       </c>
       <c r="C55">
-        <v>24.59683331930503</v>
+        <v>24.22629905152475</v>
       </c>
       <c r="D55">
-        <v>37.29883331930503</v>
+        <v>37.36229905152476</v>
       </c>
       <c r="E55">
-        <v>8.202000000000002</v>
+        <v>8.636000000000003</v>
       </c>
       <c r="F55">
-        <v>23.002</v>
+        <v>23.436</v>
       </c>
       <c r="G55">
         <v>10.3</v>
@@ -5797,28 +5797,28 @@
         <v>9.84</v>
       </c>
       <c r="M55">
-        <v>1.230607</v>
+        <v>1.253826</v>
       </c>
       <c r="N55">
-        <v>8.609393000000001</v>
+        <v>8.586174</v>
       </c>
       <c r="O55">
-        <v>1.937113425</v>
+        <v>1.93188915</v>
       </c>
       <c r="P55">
-        <v>6.672279575000001</v>
+        <v>6.65428485</v>
       </c>
       <c r="Q55">
-        <v>8.832279575000001</v>
+        <v>8.81428485</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3197044347161164</v>
+        <v>0.3249439400020014</v>
       </c>
       <c r="T55">
-        <v>1.909782936575725</v>
+        <v>1.946315086197371</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.996053979865222</v>
+        <v>7.847978906164013</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1718639624009207</v>
+        <v>0.1714917154852666</v>
       </c>
       <c r="C56">
-        <v>24.22629905152475</v>
+        <v>23.85598113177205</v>
       </c>
       <c r="D56">
-        <v>37.36229905152476</v>
+        <v>37.42598113177205</v>
       </c>
       <c r="E56">
-        <v>8.636000000000003</v>
+        <v>9.070000000000004</v>
       </c>
       <c r="F56">
-        <v>23.436</v>
+        <v>23.87</v>
       </c>
       <c r="G56">
         <v>10.3</v>
@@ -5879,28 +5879,28 @@
         <v>9.84</v>
       </c>
       <c r="M56">
-        <v>1.253826</v>
+        <v>1.277045</v>
       </c>
       <c r="N56">
-        <v>8.586174</v>
+        <v>8.562954999999999</v>
       </c>
       <c r="O56">
-        <v>1.93188915</v>
+        <v>1.926664875</v>
       </c>
       <c r="P56">
-        <v>6.65428485</v>
+        <v>6.636290124999999</v>
       </c>
       <c r="Q56">
-        <v>8.81428485</v>
+        <v>8.796290124999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3249439400020014</v>
+        <v>0.3304163121894814</v>
       </c>
       <c r="T56">
-        <v>1.946315086197371</v>
+        <v>1.984470886913313</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.847978906164013</v>
+        <v>7.705288380597393</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1714917154852666</v>
+        <v>0.1714666685696126</v>
       </c>
       <c r="C57">
-        <v>23.85598113177205</v>
+        <v>23.42627382446333</v>
       </c>
       <c r="D57">
-        <v>37.42598113177205</v>
+        <v>37.43027382446333</v>
       </c>
       <c r="E57">
-        <v>9.070000000000004</v>
+        <v>9.504000000000005</v>
       </c>
       <c r="F57">
-        <v>23.87</v>
+        <v>24.30400000000001</v>
       </c>
       <c r="G57">
         <v>10.3</v>
@@ -5961,45 +5961,45 @@
         <v>9.84</v>
       </c>
       <c r="M57">
-        <v>1.277045</v>
+        <v>1.3197072</v>
       </c>
       <c r="N57">
-        <v>8.562954999999999</v>
+        <v>8.5202928</v>
       </c>
       <c r="O57">
-        <v>1.926664875</v>
+        <v>1.91706588</v>
       </c>
       <c r="P57">
-        <v>6.636290124999999</v>
+        <v>6.60322692</v>
       </c>
       <c r="Q57">
-        <v>8.796290124999999</v>
+        <v>8.763226920000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3304163121894814</v>
+        <v>0.3361374285673013</v>
       </c>
       <c r="T57">
-        <v>1.984470886913313</v>
+        <v>2.024361042207252</v>
       </c>
       <c r="U57">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V57">
         <v>0.225</v>
       </c>
       <c r="W57">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y57">
-        <v>7.705288380597393</v>
+        <v>7.456199375134119</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1714666685696126</v>
+        <v>0.1711006216539585</v>
       </c>
       <c r="C58">
-        <v>23.42627382446333</v>
+        <v>23.05512171493509</v>
       </c>
       <c r="D58">
-        <v>37.43027382446333</v>
+        <v>37.4931217149351</v>
       </c>
       <c r="E58">
-        <v>9.504000000000005</v>
+        <v>9.938000000000006</v>
       </c>
       <c r="F58">
-        <v>24.30400000000001</v>
+        <v>24.73800000000001</v>
       </c>
       <c r="G58">
         <v>10.3</v>
@@ -6043,28 +6043,28 @@
         <v>9.84</v>
       </c>
       <c r="M58">
-        <v>1.3197072</v>
+        <v>1.3432734</v>
       </c>
       <c r="N58">
-        <v>8.5202928</v>
+        <v>8.496726599999999</v>
       </c>
       <c r="O58">
-        <v>1.91706588</v>
+        <v>1.911763485</v>
       </c>
       <c r="P58">
-        <v>6.60322692</v>
+        <v>6.584963114999999</v>
       </c>
       <c r="Q58">
-        <v>8.763226920000001</v>
+        <v>8.744963114999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3361374285673013</v>
+        <v>0.3421246433812989</v>
       </c>
       <c r="T58">
-        <v>2.024361042207252</v>
+        <v>2.066106553561374</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.456199375134119</v>
+        <v>7.325388859780888</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1711006216539585</v>
+        <v>0.1707345747383045</v>
       </c>
       <c r="C59">
-        <v>23.05512171493509</v>
+        <v>22.68418101185181</v>
       </c>
       <c r="D59">
-        <v>37.4931217149351</v>
+        <v>37.55618101185181</v>
       </c>
       <c r="E59">
-        <v>9.938000000000006</v>
+        <v>10.37200000000001</v>
       </c>
       <c r="F59">
-        <v>24.73800000000001</v>
+        <v>25.17200000000001</v>
       </c>
       <c r="G59">
         <v>10.3</v>
@@ -6125,28 +6125,28 @@
         <v>9.84</v>
       </c>
       <c r="M59">
-        <v>1.3432734</v>
+        <v>1.3668396</v>
       </c>
       <c r="N59">
-        <v>8.496726599999999</v>
+        <v>8.473160399999999</v>
       </c>
       <c r="O59">
-        <v>1.911763485</v>
+        <v>1.90646109</v>
       </c>
       <c r="P59">
-        <v>6.584963114999999</v>
+        <v>6.56669931</v>
       </c>
       <c r="Q59">
-        <v>8.744963114999999</v>
+        <v>8.726699310000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3421246433812989</v>
+        <v>0.3483969636626297</v>
       </c>
       <c r="T59">
-        <v>2.066106553561374</v>
+        <v>2.10983994640855</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.325388859780888</v>
+        <v>7.199089051853631</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1707345747383045</v>
+        <v>0.1703685278226504</v>
       </c>
       <c r="C60">
-        <v>22.68418101185182</v>
+        <v>22.31345278369754</v>
       </c>
       <c r="D60">
-        <v>37.55618101185181</v>
+        <v>37.61945278369753</v>
       </c>
       <c r="E60">
-        <v>10.372</v>
+        <v>10.806</v>
       </c>
       <c r="F60">
-        <v>25.172</v>
+        <v>25.606</v>
       </c>
       <c r="G60">
         <v>10.3</v>
@@ -6207,28 +6207,28 @@
         <v>9.84</v>
       </c>
       <c r="M60">
-        <v>1.3668396</v>
+        <v>1.3904058</v>
       </c>
       <c r="N60">
-        <v>8.473160399999999</v>
+        <v>8.4495942</v>
       </c>
       <c r="O60">
-        <v>1.90646109</v>
+        <v>1.901158695</v>
       </c>
       <c r="P60">
-        <v>6.56669931</v>
+        <v>6.548435505</v>
       </c>
       <c r="Q60">
-        <v>8.726699310000001</v>
+        <v>8.708435505000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3483969636626297</v>
+        <v>0.3549752507869523</v>
       </c>
       <c r="T60">
-        <v>2.109839946408549</v>
+        <v>2.155706675492173</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.199089051853633</v>
+        <v>7.077070593347639</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1703685278226504</v>
+        <v>0.1700024809069964</v>
       </c>
       <c r="C61">
-        <v>22.31345278369754</v>
+        <v>21.94293810616889</v>
       </c>
       <c r="D61">
-        <v>37.61945278369753</v>
+        <v>37.68293810616888</v>
       </c>
       <c r="E61">
-        <v>10.806</v>
+        <v>11.24</v>
       </c>
       <c r="F61">
-        <v>25.606</v>
+        <v>26.04</v>
       </c>
       <c r="G61">
         <v>10.3</v>
@@ -6289,28 +6289,28 @@
         <v>9.84</v>
       </c>
       <c r="M61">
-        <v>1.3904058</v>
+        <v>1.413972</v>
       </c>
       <c r="N61">
-        <v>8.4495942</v>
+        <v>8.426027999999999</v>
       </c>
       <c r="O61">
-        <v>1.901158695</v>
+        <v>1.8958563</v>
       </c>
       <c r="P61">
-        <v>6.548435505</v>
+        <v>6.530171699999999</v>
       </c>
       <c r="Q61">
-        <v>8.708435505000001</v>
+        <v>8.690171699999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3549752507869523</v>
+        <v>0.361882452267491</v>
       </c>
       <c r="T61">
-        <v>2.155706675492173</v>
+        <v>2.203866741029977</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.077070593347639</v>
+        <v>6.959119416791844</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1700024809069964</v>
+        <v>0.1696364339913424</v>
       </c>
       <c r="C62">
-        <v>21.94293810616889</v>
+        <v>21.572638062236</v>
       </c>
       <c r="D62">
-        <v>37.68293810616888</v>
+        <v>37.746638062236</v>
       </c>
       <c r="E62">
-        <v>11.24</v>
+        <v>11.674</v>
       </c>
       <c r="F62">
-        <v>26.04</v>
+        <v>26.474</v>
       </c>
       <c r="G62">
         <v>10.3</v>
@@ -6371,28 +6371,28 @@
         <v>9.84</v>
       </c>
       <c r="M62">
-        <v>1.413972</v>
+        <v>1.4375382</v>
       </c>
       <c r="N62">
-        <v>8.426027999999999</v>
+        <v>8.402461799999999</v>
       </c>
       <c r="O62">
-        <v>1.8958563</v>
+        <v>1.890553905</v>
       </c>
       <c r="P62">
-        <v>6.530171699999999</v>
+        <v>6.511907894999999</v>
       </c>
       <c r="Q62">
-        <v>8.690171699999999</v>
+        <v>8.671907895</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.361882452267491</v>
+        <v>0.3691438692085702</v>
       </c>
       <c r="T62">
-        <v>2.203866741029977</v>
+        <v>2.254496553518439</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.959119416791844</v>
+        <v>6.845035491926404</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1696364339913424</v>
+        <v>0.1692703870756883</v>
       </c>
       <c r="C63">
-        <v>21.572638062236</v>
+        <v>21.20255374220411</v>
       </c>
       <c r="D63">
-        <v>37.746638062236</v>
+        <v>37.81055374220411</v>
       </c>
       <c r="E63">
-        <v>11.674</v>
+        <v>12.108</v>
       </c>
       <c r="F63">
-        <v>26.474</v>
+        <v>26.908</v>
       </c>
       <c r="G63">
         <v>10.3</v>
@@ -6453,28 +6453,28 @@
         <v>9.84</v>
       </c>
       <c r="M63">
-        <v>1.4375382</v>
+        <v>1.4611044</v>
       </c>
       <c r="N63">
-        <v>8.402461799999999</v>
+        <v>8.3788956</v>
       </c>
       <c r="O63">
-        <v>1.890553905</v>
+        <v>1.88525151</v>
       </c>
       <c r="P63">
-        <v>6.511907894999999</v>
+        <v>6.49364409</v>
       </c>
       <c r="Q63">
-        <v>8.671907895</v>
+        <v>8.65364409</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3691438692085702</v>
+        <v>0.3767874659886535</v>
       </c>
       <c r="T63">
-        <v>2.254496553518439</v>
+        <v>2.307791092979976</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.845035491926404</v>
+        <v>6.734631693669527</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1692703870756883</v>
+        <v>0.1689043401600343</v>
       </c>
       <c r="C64">
-        <v>21.20255374220411</v>
+        <v>20.83268624377574</v>
       </c>
       <c r="D64">
-        <v>37.81055374220411</v>
+        <v>37.87468624377573</v>
       </c>
       <c r="E64">
-        <v>12.108</v>
+        <v>12.542</v>
       </c>
       <c r="F64">
-        <v>26.908</v>
+        <v>27.342</v>
       </c>
       <c r="G64">
         <v>10.3</v>
@@ -6535,28 +6535,28 @@
         <v>9.84</v>
       </c>
       <c r="M64">
-        <v>1.4611044</v>
+        <v>1.4846706</v>
       </c>
       <c r="N64">
-        <v>8.3788956</v>
+        <v>8.3553294</v>
       </c>
       <c r="O64">
-        <v>1.88525151</v>
+        <v>1.879949115</v>
       </c>
       <c r="P64">
-        <v>6.49364409</v>
+        <v>6.475380285</v>
       </c>
       <c r="Q64">
-        <v>8.65364409</v>
+        <v>8.635380285</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3767874659886535</v>
+        <v>0.3848442301622548</v>
       </c>
       <c r="T64">
-        <v>2.307791092979976</v>
+        <v>2.363966418358354</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.734631693669527</v>
+        <v>6.627732777896997</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1689043401600343</v>
+        <v>0.1685382932443803</v>
       </c>
       <c r="C65">
-        <v>20.83268624377574</v>
+        <v>20.46303667211351</v>
       </c>
       <c r="D65">
-        <v>37.87468624377573</v>
+        <v>37.93903667211351</v>
       </c>
       <c r="E65">
-        <v>12.542</v>
+        <v>12.976</v>
       </c>
       <c r="F65">
-        <v>27.342</v>
+        <v>27.776</v>
       </c>
       <c r="G65">
         <v>10.3</v>
@@ -6617,28 +6617,28 @@
         <v>9.84</v>
       </c>
       <c r="M65">
-        <v>1.4846706</v>
+        <v>1.5082368</v>
       </c>
       <c r="N65">
-        <v>8.3553294</v>
+        <v>8.331763199999999</v>
       </c>
       <c r="O65">
-        <v>1.879949115</v>
+        <v>1.87464672</v>
       </c>
       <c r="P65">
-        <v>6.475380285</v>
+        <v>6.45711648</v>
       </c>
       <c r="Q65">
-        <v>8.635380285</v>
+        <v>8.61711648</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3848442301622548</v>
+        <v>0.3933485923455008</v>
       </c>
       <c r="T65">
-        <v>2.363966418358354</v>
+        <v>2.423262595146642</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.627732777896997</v>
+        <v>6.524174453242354</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1685382932443803</v>
+        <v>0.1681722463287262</v>
       </c>
       <c r="C66">
-        <v>20.46303667211351</v>
+        <v>20.09360613990377</v>
       </c>
       <c r="D66">
-        <v>37.93903667211351</v>
+        <v>38.00360613990378</v>
       </c>
       <c r="E66">
-        <v>12.976</v>
+        <v>13.41</v>
       </c>
       <c r="F66">
-        <v>27.776</v>
+        <v>28.21</v>
       </c>
       <c r="G66">
         <v>10.3</v>
@@ -6699,28 +6699,28 @@
         <v>9.84</v>
       </c>
       <c r="M66">
-        <v>1.5082368</v>
+        <v>1.531803</v>
       </c>
       <c r="N66">
-        <v>8.331763199999999</v>
+        <v>8.308197</v>
       </c>
       <c r="O66">
-        <v>1.87464672</v>
+        <v>1.869344325</v>
       </c>
       <c r="P66">
-        <v>6.45711648</v>
+        <v>6.438852675</v>
       </c>
       <c r="Q66">
-        <v>8.61711648</v>
+        <v>8.598852675</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3933485923455008</v>
+        <v>0.4023389180820749</v>
       </c>
       <c r="T66">
-        <v>2.423262595146642</v>
+        <v>2.48594712489426</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.524174453242354</v>
+        <v>6.423802538577087</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1681722463287262</v>
+        <v>0.1678061994130722</v>
       </c>
       <c r="C67">
-        <v>20.09360613990377</v>
+        <v>19.72439576742053</v>
       </c>
       <c r="D67">
-        <v>38.00360613990378</v>
+        <v>38.06839576742054</v>
       </c>
       <c r="E67">
-        <v>13.41</v>
+        <v>13.844</v>
       </c>
       <c r="F67">
-        <v>28.21</v>
+        <v>28.64400000000001</v>
       </c>
       <c r="G67">
         <v>10.3</v>
@@ -6781,28 +6781,28 @@
         <v>9.84</v>
       </c>
       <c r="M67">
-        <v>1.531803</v>
+        <v>1.5553692</v>
       </c>
       <c r="N67">
-        <v>8.308197</v>
+        <v>8.284630799999999</v>
       </c>
       <c r="O67">
-        <v>1.869344325</v>
+        <v>1.86404193</v>
       </c>
       <c r="P67">
-        <v>6.438852675</v>
+        <v>6.420588869999999</v>
       </c>
       <c r="Q67">
-        <v>8.598852675</v>
+        <v>8.58058887</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4023389180820749</v>
+        <v>0.4118580865090359</v>
       </c>
       <c r="T67">
-        <v>2.48594712489426</v>
+        <v>2.552318979921151</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.423802538577087</v>
+        <v>6.326472197083494</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1678061994130722</v>
+        <v>0.1674401524974182</v>
       </c>
       <c r="C68">
-        <v>19.72439576742053</v>
+        <v>19.35540668259041</v>
       </c>
       <c r="D68">
-        <v>38.06839576742054</v>
+        <v>38.13340668259041</v>
       </c>
       <c r="E68">
-        <v>13.844</v>
+        <v>14.27800000000001</v>
       </c>
       <c r="F68">
-        <v>28.64400000000001</v>
+        <v>29.07800000000001</v>
       </c>
       <c r="G68">
         <v>10.3</v>
@@ -6863,28 +6863,28 @@
         <v>9.84</v>
       </c>
       <c r="M68">
-        <v>1.5553692</v>
+        <v>1.5789354</v>
       </c>
       <c r="N68">
-        <v>8.284630799999999</v>
+        <v>8.261064599999999</v>
       </c>
       <c r="O68">
-        <v>1.86404193</v>
+        <v>1.858739535</v>
       </c>
       <c r="P68">
-        <v>6.420588869999999</v>
+        <v>6.402325064999999</v>
       </c>
       <c r="Q68">
-        <v>8.58058887</v>
+        <v>8.562325065</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4118580865090359</v>
+        <v>0.4219541742346006</v>
       </c>
       <c r="T68">
-        <v>2.552318979921151</v>
+        <v>2.622713371616337</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.326472197083494</v>
+        <v>6.232047238918069</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1674401524974182</v>
+        <v>0.1670741055817641</v>
       </c>
       <c r="C69">
-        <v>19.35540668259041</v>
+        <v>18.98664002105796</v>
       </c>
       <c r="D69">
-        <v>38.13340668259041</v>
+        <v>38.19864002105797</v>
       </c>
       <c r="E69">
-        <v>14.27800000000001</v>
+        <v>14.71200000000001</v>
       </c>
       <c r="F69">
-        <v>29.07800000000001</v>
+        <v>29.51200000000001</v>
       </c>
       <c r="G69">
         <v>10.3</v>
@@ -6945,28 +6945,28 @@
         <v>9.84</v>
       </c>
       <c r="M69">
-        <v>1.5789354</v>
+        <v>1.602501600000001</v>
       </c>
       <c r="N69">
-        <v>8.261064599999999</v>
+        <v>8.2374984</v>
       </c>
       <c r="O69">
-        <v>1.858739535</v>
+        <v>1.85343714</v>
       </c>
       <c r="P69">
-        <v>6.402325064999999</v>
+        <v>6.384061259999999</v>
       </c>
       <c r="Q69">
-        <v>8.562325065</v>
+        <v>8.544061259999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4219541742346006</v>
+        <v>0.432681267443013</v>
       </c>
       <c r="T69">
-        <v>2.622713371616337</v>
+        <v>2.697507412792473</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.232047238918069</v>
+        <v>6.140399485404568</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1670741055817641</v>
+        <v>0.1672428086661101</v>
       </c>
       <c r="C70">
-        <v>18.98664002105796</v>
+        <v>18.52254768478478</v>
       </c>
       <c r="D70">
-        <v>38.19864002105797</v>
+        <v>38.16854768478478</v>
       </c>
       <c r="E70">
-        <v>14.71200000000001</v>
+        <v>15.146</v>
       </c>
       <c r="F70">
-        <v>29.51200000000001</v>
+        <v>29.94600000000001</v>
       </c>
       <c r="G70">
         <v>10.3</v>
@@ -7027,45 +7027,45 @@
         <v>9.84</v>
       </c>
       <c r="M70">
-        <v>1.602501600000001</v>
+        <v>1.6560138</v>
       </c>
       <c r="N70">
-        <v>8.2374984</v>
+        <v>8.1839862</v>
       </c>
       <c r="O70">
-        <v>1.85343714</v>
+        <v>1.841396895</v>
       </c>
       <c r="P70">
-        <v>6.384061259999999</v>
+        <v>6.342589305</v>
       </c>
       <c r="Q70">
-        <v>8.544061259999999</v>
+        <v>8.502589305000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.432681267443013</v>
+        <v>0.4441004311810003</v>
       </c>
       <c r="T70">
-        <v>2.697507412792473</v>
+        <v>2.777126875979972</v>
       </c>
       <c r="U70">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V70">
         <v>0.225</v>
       </c>
       <c r="W70">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>6.140399485404568</v>
+        <v>5.941979469011669</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1672428086661101</v>
+        <v>0.166884511750456</v>
       </c>
       <c r="C71">
-        <v>18.52254768478478</v>
+        <v>18.15251541258073</v>
       </c>
       <c r="D71">
-        <v>38.16854768478478</v>
+        <v>38.23251541258074</v>
       </c>
       <c r="E71">
-        <v>15.146</v>
+        <v>15.58000000000001</v>
       </c>
       <c r="F71">
-        <v>29.94600000000001</v>
+        <v>30.38000000000001</v>
       </c>
       <c r="G71">
         <v>10.3</v>
@@ -7109,28 +7109,28 @@
         <v>9.84</v>
       </c>
       <c r="M71">
-        <v>1.6560138</v>
+        <v>1.680014</v>
       </c>
       <c r="N71">
-        <v>8.1839862</v>
+        <v>8.159986</v>
       </c>
       <c r="O71">
-        <v>1.841396895</v>
+        <v>1.83599685</v>
       </c>
       <c r="P71">
-        <v>6.342589305</v>
+        <v>6.32398915</v>
       </c>
       <c r="Q71">
-        <v>8.502589305000001</v>
+        <v>8.483989149999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4441004311810003</v>
+        <v>0.4562808725015202</v>
       </c>
       <c r="T71">
-        <v>2.777126875979972</v>
+        <v>2.862054303379971</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.941979469011669</v>
+        <v>5.85709404802579</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.166884511750456</v>
+        <v>0.166526214834802</v>
       </c>
       <c r="C72">
-        <v>18.15251541258073</v>
+        <v>17.78269791089529</v>
       </c>
       <c r="D72">
-        <v>38.23251541258074</v>
+        <v>38.2966979108953</v>
       </c>
       <c r="E72">
-        <v>15.58000000000001</v>
+        <v>16.01400000000001</v>
       </c>
       <c r="F72">
-        <v>30.38000000000001</v>
+        <v>30.81400000000001</v>
       </c>
       <c r="G72">
         <v>10.3</v>
@@ -7191,28 +7191,28 @@
         <v>9.84</v>
       </c>
       <c r="M72">
-        <v>1.680014</v>
+        <v>1.7040142</v>
       </c>
       <c r="N72">
-        <v>8.159986</v>
+        <v>8.1359858</v>
       </c>
       <c r="O72">
-        <v>1.83599685</v>
+        <v>1.830596805</v>
       </c>
       <c r="P72">
-        <v>6.32398915</v>
+        <v>6.305388995</v>
       </c>
       <c r="Q72">
-        <v>8.483989149999999</v>
+        <v>8.465388995000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4562808725015202</v>
+        <v>0.469301344257938</v>
       </c>
       <c r="T72">
-        <v>2.862054303379971</v>
+        <v>2.952838794738591</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.85709404802579</v>
+        <v>5.774599765659229</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.166526214834802</v>
+        <v>0.166167917919148</v>
       </c>
       <c r="C73">
-        <v>17.78269791089528</v>
+        <v>17.41309626317964</v>
       </c>
       <c r="D73">
-        <v>38.29669791089529</v>
+        <v>38.36109626317965</v>
       </c>
       <c r="E73">
-        <v>16.014</v>
+        <v>16.448</v>
       </c>
       <c r="F73">
-        <v>30.814</v>
+        <v>31.248</v>
       </c>
       <c r="G73">
         <v>10.3</v>
@@ -7273,28 +7273,28 @@
         <v>9.84</v>
       </c>
       <c r="M73">
-        <v>1.7040142</v>
+        <v>1.7280144</v>
       </c>
       <c r="N73">
-        <v>8.1359858</v>
+        <v>8.111985599999999</v>
       </c>
       <c r="O73">
-        <v>1.830596805</v>
+        <v>1.82519676</v>
       </c>
       <c r="P73">
-        <v>6.305388995</v>
+        <v>6.286788839999999</v>
       </c>
       <c r="Q73">
-        <v>8.465388995000001</v>
+        <v>8.44678884</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4693013442579379</v>
+        <v>0.4832518497112428</v>
       </c>
       <c r="T73">
-        <v>2.95283879473859</v>
+        <v>3.050107892622826</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.77459976565923</v>
+        <v>5.694396991136183</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.166167917919148</v>
+        <v>0.1658096210034939</v>
       </c>
       <c r="C74">
-        <v>17.41309626317964</v>
+        <v>17.04371156018482</v>
       </c>
       <c r="D74">
-        <v>38.36109626317965</v>
+        <v>38.42571156018482</v>
       </c>
       <c r="E74">
-        <v>16.448</v>
+        <v>16.882</v>
       </c>
       <c r="F74">
-        <v>31.248</v>
+        <v>31.682</v>
       </c>
       <c r="G74">
         <v>10.3</v>
@@ -7355,28 +7355,28 @@
         <v>9.84</v>
       </c>
       <c r="M74">
-        <v>1.7280144</v>
+        <v>1.7520146</v>
       </c>
       <c r="N74">
-        <v>8.111985599999999</v>
+        <v>8.087985399999999</v>
       </c>
       <c r="O74">
-        <v>1.82519676</v>
+        <v>1.819796715</v>
       </c>
       <c r="P74">
-        <v>6.286788839999999</v>
+        <v>6.268188684999999</v>
       </c>
       <c r="Q74">
-        <v>8.44678884</v>
+        <v>8.428188684999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4832518497112428</v>
+        <v>0.4982357259388664</v>
       </c>
       <c r="T74">
-        <v>3.050107892622826</v>
+        <v>3.154582108868856</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.694396991136183</v>
+        <v>5.616391552901442</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1658096210034939</v>
+        <v>0.1654513240878399</v>
       </c>
       <c r="C75">
-        <v>17.04371156018482</v>
+        <v>16.67454490002326</v>
       </c>
       <c r="D75">
-        <v>38.42571156018482</v>
+        <v>38.49054490002326</v>
       </c>
       <c r="E75">
-        <v>16.882</v>
+        <v>17.31600000000001</v>
       </c>
       <c r="F75">
-        <v>31.682</v>
+        <v>32.11600000000001</v>
       </c>
       <c r="G75">
         <v>10.3</v>
@@ -7437,28 +7437,28 @@
         <v>9.84</v>
       </c>
       <c r="M75">
-        <v>1.7520146</v>
+        <v>1.7760148</v>
       </c>
       <c r="N75">
-        <v>8.087985399999999</v>
+        <v>8.063985199999999</v>
       </c>
       <c r="O75">
-        <v>1.819796715</v>
+        <v>1.81439667</v>
       </c>
       <c r="P75">
-        <v>6.268188684999999</v>
+        <v>6.24958853</v>
       </c>
       <c r="Q75">
-        <v>8.428188684999999</v>
+        <v>8.409588530000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4982357259388664</v>
+        <v>0.5143722080301534</v>
       </c>
       <c r="T75">
-        <v>3.154582108868856</v>
+        <v>3.267092803287658</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.616391552901442</v>
+        <v>5.540494369754124</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1654513240878399</v>
+        <v>0.1650930271721859</v>
       </c>
       <c r="C76">
-        <v>16.67454490002326</v>
+        <v>16.30559738823106</v>
       </c>
       <c r="D76">
-        <v>38.49054490002326</v>
+        <v>38.55559738823106</v>
       </c>
       <c r="E76">
-        <v>17.31600000000001</v>
+        <v>17.75</v>
       </c>
       <c r="F76">
-        <v>32.11600000000001</v>
+        <v>32.55</v>
       </c>
       <c r="G76">
         <v>10.3</v>
@@ -7519,28 +7519,28 @@
         <v>9.84</v>
       </c>
       <c r="M76">
-        <v>1.7760148</v>
+        <v>1.800015</v>
       </c>
       <c r="N76">
-        <v>8.063985199999999</v>
+        <v>8.039985</v>
       </c>
       <c r="O76">
-        <v>1.81439667</v>
+        <v>1.808996625</v>
       </c>
       <c r="P76">
-        <v>6.24958853</v>
+        <v>6.230988375</v>
       </c>
       <c r="Q76">
-        <v>8.409588530000001</v>
+        <v>8.390988374999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5143722080301534</v>
+        <v>0.5317996086887434</v>
       </c>
       <c r="T76">
-        <v>3.267092803287658</v>
+        <v>3.388604353259965</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.540494369754124</v>
+        <v>5.466621111490737</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1650930271721859</v>
+        <v>0.1647347302565318</v>
       </c>
       <c r="C77">
-        <v>16.30559738823106</v>
+        <v>15.93687013783079</v>
       </c>
       <c r="D77">
-        <v>38.55559738823106</v>
+        <v>38.62087013783079</v>
       </c>
       <c r="E77">
-        <v>17.75</v>
+        <v>18.184</v>
       </c>
       <c r="F77">
-        <v>32.55</v>
+        <v>32.984</v>
       </c>
       <c r="G77">
         <v>10.3</v>
@@ -7601,28 +7601,28 @@
         <v>9.84</v>
       </c>
       <c r="M77">
-        <v>1.800015</v>
+        <v>1.8240152</v>
       </c>
       <c r="N77">
-        <v>8.039985</v>
+        <v>8.0159848</v>
       </c>
       <c r="O77">
-        <v>1.808996625</v>
+        <v>1.80359658</v>
       </c>
       <c r="P77">
-        <v>6.230988375</v>
+        <v>6.21238822</v>
       </c>
       <c r="Q77">
-        <v>8.390988374999999</v>
+        <v>8.372388220000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5317996086887434</v>
+        <v>0.5506792927355493</v>
       </c>
       <c r="T77">
-        <v>3.388604353259965</v>
+        <v>3.520241865729964</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.466621111490737</v>
+        <v>5.394691886339544</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1647347302565318</v>
+        <v>0.1643764333408778</v>
       </c>
       <c r="C78">
-        <v>15.93687013783079</v>
+        <v>15.56836426939495</v>
       </c>
       <c r="D78">
-        <v>38.62087013783079</v>
+        <v>38.68636426939496</v>
       </c>
       <c r="E78">
-        <v>18.184</v>
+        <v>18.61800000000001</v>
       </c>
       <c r="F78">
-        <v>32.984</v>
+        <v>33.41800000000001</v>
       </c>
       <c r="G78">
         <v>10.3</v>
@@ -7683,28 +7683,28 @@
         <v>9.84</v>
       </c>
       <c r="M78">
-        <v>1.8240152</v>
+        <v>1.8480154</v>
       </c>
       <c r="N78">
-        <v>8.0159848</v>
+        <v>7.991984599999999</v>
       </c>
       <c r="O78">
-        <v>1.80359658</v>
+        <v>1.798196535</v>
       </c>
       <c r="P78">
-        <v>6.21238822</v>
+        <v>6.193788065</v>
       </c>
       <c r="Q78">
-        <v>8.372388220000001</v>
+        <v>8.353788065</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5506792927355493</v>
+        <v>0.5712006884385991</v>
       </c>
       <c r="T78">
-        <v>3.520241865729964</v>
+        <v>3.663326118414745</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.394691886339544</v>
+        <v>5.324630952750717</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1643764333408778</v>
+        <v>0.1640181364252237</v>
       </c>
       <c r="C79">
-        <v>15.56836426939495</v>
+        <v>15.20008091111016</v>
       </c>
       <c r="D79">
-        <v>38.68636426939496</v>
+        <v>38.75208091111017</v>
       </c>
       <c r="E79">
-        <v>18.61800000000001</v>
+        <v>19.052</v>
       </c>
       <c r="F79">
-        <v>33.41800000000001</v>
+        <v>33.852</v>
       </c>
       <c r="G79">
         <v>10.3</v>
@@ -7765,28 +7765,28 @@
         <v>9.84</v>
       </c>
       <c r="M79">
-        <v>1.8480154</v>
+        <v>1.8720156</v>
       </c>
       <c r="N79">
-        <v>7.991984599999999</v>
+        <v>7.9679844</v>
       </c>
       <c r="O79">
-        <v>1.798196535</v>
+        <v>1.79279649</v>
       </c>
       <c r="P79">
-        <v>6.193788065</v>
+        <v>6.17518791</v>
       </c>
       <c r="Q79">
-        <v>8.353788065</v>
+        <v>8.33518791</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5712006884385991</v>
+        <v>0.5935876655691988</v>
       </c>
       <c r="T79">
-        <v>3.663326118414745</v>
+        <v>3.819418030434507</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.324630952750717</v>
+        <v>5.256366453356478</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1640181364252237</v>
+        <v>0.1636598395095697</v>
       </c>
       <c r="C80">
-        <v>15.20008091111016</v>
+        <v>14.83202119884186</v>
       </c>
       <c r="D80">
-        <v>38.75208091111017</v>
+        <v>38.81802119884188</v>
       </c>
       <c r="E80">
-        <v>19.052</v>
+        <v>19.48600000000001</v>
       </c>
       <c r="F80">
-        <v>33.852</v>
+        <v>34.28600000000001</v>
       </c>
       <c r="G80">
         <v>10.3</v>
@@ -7847,28 +7847,28 @@
         <v>9.84</v>
       </c>
       <c r="M80">
-        <v>1.8720156</v>
+        <v>1.8960158</v>
       </c>
       <c r="N80">
-        <v>7.9679844</v>
+        <v>7.943984199999999</v>
       </c>
       <c r="O80">
-        <v>1.79279649</v>
+        <v>1.787396445</v>
       </c>
       <c r="P80">
-        <v>6.17518791</v>
+        <v>6.156587754999999</v>
       </c>
       <c r="Q80">
-        <v>8.33518791</v>
+        <v>8.316587755</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5935876655691988</v>
+        <v>0.6181067357598559</v>
       </c>
       <c r="T80">
-        <v>3.819418030434507</v>
+        <v>3.990375838837103</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.256366453356478</v>
+        <v>5.189830169136775</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1636598395095697</v>
+        <v>0.1633015425939157</v>
       </c>
       <c r="C81">
-        <v>14.83202119884186</v>
+        <v>14.46418627619985</v>
       </c>
       <c r="D81">
-        <v>38.81802119884188</v>
+        <v>38.88418627619986</v>
       </c>
       <c r="E81">
-        <v>19.48600000000001</v>
+        <v>19.92000000000001</v>
       </c>
       <c r="F81">
-        <v>34.28600000000001</v>
+        <v>34.72000000000001</v>
       </c>
       <c r="G81">
         <v>10.3</v>
@@ -7929,28 +7929,28 @@
         <v>9.84</v>
       </c>
       <c r="M81">
-        <v>1.8960158</v>
+        <v>1.920016</v>
       </c>
       <c r="N81">
-        <v>7.943984199999999</v>
+        <v>7.919983999999999</v>
       </c>
       <c r="O81">
-        <v>1.787396445</v>
+        <v>1.7819964</v>
       </c>
       <c r="P81">
-        <v>6.156587754999999</v>
+        <v>6.1379876</v>
       </c>
       <c r="Q81">
-        <v>8.316587755</v>
+        <v>8.297987599999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6181067357598559</v>
+        <v>0.6450777129695785</v>
       </c>
       <c r="T81">
-        <v>3.990375838837103</v>
+        <v>4.178429428079959</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.189830169136775</v>
+        <v>5.124957292022565</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1633015425939157</v>
+        <v>0.1629432456782616</v>
       </c>
       <c r="C82">
-        <v>14.46418627619985</v>
+        <v>14.09657729460428</v>
       </c>
       <c r="D82">
-        <v>38.88418627619986</v>
+        <v>38.95057729460428</v>
       </c>
       <c r="E82">
-        <v>19.92000000000001</v>
+        <v>20.354</v>
       </c>
       <c r="F82">
-        <v>34.72000000000001</v>
+        <v>35.154</v>
       </c>
       <c r="G82">
         <v>10.3</v>
@@ -8011,28 +8011,28 @@
         <v>9.84</v>
       </c>
       <c r="M82">
-        <v>1.920016</v>
+        <v>1.9440162</v>
       </c>
       <c r="N82">
-        <v>7.919983999999999</v>
+        <v>7.8959838</v>
       </c>
       <c r="O82">
-        <v>1.7819964</v>
+        <v>1.776596355</v>
       </c>
       <c r="P82">
-        <v>6.1379876</v>
+        <v>6.119387445</v>
       </c>
       <c r="Q82">
-        <v>8.297987599999999</v>
+        <v>8.279387445000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6450777129695785</v>
+        <v>0.6748877404119035</v>
       </c>
       <c r="T82">
-        <v>4.178429428079959</v>
+        <v>4.386278131979956</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.124957292022565</v>
+        <v>5.061686214343275</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1629432456782616</v>
+        <v>0.1625849487626076</v>
       </c>
       <c r="C83">
-        <v>14.09657729460428</v>
+        <v>13.72919541335251</v>
       </c>
       <c r="D83">
-        <v>38.95057729460428</v>
+        <v>39.01719541335252</v>
       </c>
       <c r="E83">
-        <v>20.354</v>
+        <v>20.78800000000001</v>
       </c>
       <c r="F83">
-        <v>35.154</v>
+        <v>35.58800000000001</v>
       </c>
       <c r="G83">
         <v>10.3</v>
@@ -8093,28 +8093,28 @@
         <v>9.84</v>
       </c>
       <c r="M83">
-        <v>1.9440162</v>
+        <v>1.9680164</v>
       </c>
       <c r="N83">
-        <v>7.8959838</v>
+        <v>7.871983599999999</v>
       </c>
       <c r="O83">
-        <v>1.776596355</v>
+        <v>1.77119631</v>
       </c>
       <c r="P83">
-        <v>6.119387445</v>
+        <v>6.10078729</v>
       </c>
       <c r="Q83">
-        <v>8.279387445000001</v>
+        <v>8.26078729</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6748877404119035</v>
+        <v>0.7080099931255979</v>
       </c>
       <c r="T83">
-        <v>4.386278131979956</v>
+        <v>4.617221136313287</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.061686214343275</v>
+        <v>4.999958333680551</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1625849487626076</v>
+        <v>0.1622266518469535</v>
       </c>
       <c r="C84">
-        <v>13.72919541335251</v>
+        <v>13.36204179968665</v>
       </c>
       <c r="D84">
-        <v>39.01719541335252</v>
+        <v>39.08404179968666</v>
       </c>
       <c r="E84">
-        <v>20.78800000000001</v>
+        <v>21.222</v>
       </c>
       <c r="F84">
-        <v>35.58800000000001</v>
+        <v>36.02200000000001</v>
       </c>
       <c r="G84">
         <v>10.3</v>
@@ -8175,28 +8175,28 @@
         <v>9.84</v>
       </c>
       <c r="M84">
-        <v>1.9680164</v>
+        <v>1.9920166</v>
       </c>
       <c r="N84">
-        <v>7.871983599999999</v>
+        <v>7.847983399999999</v>
       </c>
       <c r="O84">
-        <v>1.77119631</v>
+        <v>1.765796265</v>
       </c>
       <c r="P84">
-        <v>6.10078729</v>
+        <v>6.082187135</v>
       </c>
       <c r="Q84">
-        <v>8.26078729</v>
+        <v>8.242187135</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7080099931255979</v>
+        <v>0.7450289814526682</v>
       </c>
       <c r="T84">
-        <v>4.617221136313287</v>
+        <v>4.875333905862304</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.999958333680551</v>
+        <v>4.939717871828979</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1622266518469535</v>
+        <v>0.1618683549312996</v>
       </c>
       <c r="C85">
-        <v>13.36204179968665</v>
+        <v>12.9951176288616</v>
       </c>
       <c r="D85">
-        <v>39.08404179968666</v>
+        <v>39.15111762886161</v>
       </c>
       <c r="E85">
-        <v>21.222</v>
+        <v>21.65600000000001</v>
       </c>
       <c r="F85">
-        <v>36.02200000000001</v>
+        <v>36.45600000000001</v>
       </c>
       <c r="G85">
         <v>10.3</v>
@@ -8257,28 +8257,28 @@
         <v>9.84</v>
       </c>
       <c r="M85">
-        <v>1.9920166</v>
+        <v>2.0160168</v>
       </c>
       <c r="N85">
-        <v>7.847983399999999</v>
+        <v>7.823983199999999</v>
       </c>
       <c r="O85">
-        <v>1.765796265</v>
+        <v>1.76039622</v>
       </c>
       <c r="P85">
-        <v>6.082187135</v>
+        <v>6.063586979999999</v>
       </c>
       <c r="Q85">
-        <v>8.242187135</v>
+        <v>8.22358698</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7450289814526682</v>
+        <v>0.7866753433206225</v>
       </c>
       <c r="T85">
-        <v>4.875333905862304</v>
+        <v>5.16571077160495</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.939717871828979</v>
+        <v>4.880911706688157</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1618683549312995</v>
+        <v>0.1615100580156455</v>
       </c>
       <c r="C86">
-        <v>12.99511762886162</v>
+        <v>12.62842408421406</v>
       </c>
       <c r="D86">
-        <v>39.15111762886162</v>
+        <v>39.21842408421406</v>
       </c>
       <c r="E86">
-        <v>21.656</v>
+        <v>22.09</v>
       </c>
       <c r="F86">
-        <v>36.456</v>
+        <v>36.89</v>
       </c>
       <c r="G86">
         <v>10.3</v>
@@ -8339,28 +8339,28 @@
         <v>9.84</v>
       </c>
       <c r="M86">
-        <v>2.0160168</v>
+        <v>2.040017</v>
       </c>
       <c r="N86">
-        <v>7.8239832</v>
+        <v>7.799982999999999</v>
       </c>
       <c r="O86">
-        <v>1.76039622</v>
+        <v>1.754996175</v>
       </c>
       <c r="P86">
-        <v>6.06358698</v>
+        <v>6.044986825</v>
       </c>
       <c r="Q86">
-        <v>8.22358698</v>
+        <v>8.204986824999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7866753433206219</v>
+        <v>0.8338745534376366</v>
       </c>
       <c r="T86">
-        <v>5.165710771604947</v>
+        <v>5.494804552779944</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.880911706688158</v>
+        <v>4.823489216021239</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1615100580156455</v>
+        <v>0.1611517610999915</v>
       </c>
       <c r="C87">
-        <v>12.62842408421406</v>
+        <v>12.26196235723199</v>
       </c>
       <c r="D87">
-        <v>39.21842408421406</v>
+        <v>39.28596235723199</v>
       </c>
       <c r="E87">
-        <v>22.09</v>
+        <v>22.524</v>
       </c>
       <c r="F87">
-        <v>36.89</v>
+        <v>37.32400000000001</v>
       </c>
       <c r="G87">
         <v>10.3</v>
@@ -8421,28 +8421,28 @@
         <v>9.84</v>
       </c>
       <c r="M87">
-        <v>2.040017</v>
+        <v>2.0640172</v>
       </c>
       <c r="N87">
-        <v>7.799982999999999</v>
+        <v>7.7759828</v>
       </c>
       <c r="O87">
-        <v>1.754996175</v>
+        <v>1.74959613</v>
       </c>
       <c r="P87">
-        <v>6.044986825</v>
+        <v>6.026386669999999</v>
       </c>
       <c r="Q87">
-        <v>8.204986824999999</v>
+        <v>8.186386669999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8338745534376366</v>
+        <v>0.8878165078570818</v>
       </c>
       <c r="T87">
-        <v>5.494804552779944</v>
+        <v>5.870911731265654</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.823489216021239</v>
+        <v>4.767402132114015</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1611517610999915</v>
+        <v>0.1607934641843374</v>
       </c>
       <c r="C88">
-        <v>12.26196235723199</v>
+        <v>11.89573364762501</v>
       </c>
       <c r="D88">
-        <v>39.28596235723199</v>
+        <v>39.35373364762502</v>
       </c>
       <c r="E88">
-        <v>22.524</v>
+        <v>22.958</v>
       </c>
       <c r="F88">
-        <v>37.32400000000001</v>
+        <v>37.758</v>
       </c>
       <c r="G88">
         <v>10.3</v>
@@ -8503,28 +8503,28 @@
         <v>9.84</v>
       </c>
       <c r="M88">
-        <v>2.0640172</v>
+        <v>2.0880174</v>
       </c>
       <c r="N88">
-        <v>7.7759828</v>
+        <v>7.7519826</v>
       </c>
       <c r="O88">
-        <v>1.74959613</v>
+        <v>1.744196085</v>
       </c>
       <c r="P88">
-        <v>6.026386669999999</v>
+        <v>6.007786514999999</v>
       </c>
       <c r="Q88">
-        <v>8.186386669999999</v>
+        <v>8.167786515</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8878165078570818</v>
+        <v>0.9500572244949032</v>
       </c>
       <c r="T88">
-        <v>5.870911731265654</v>
+        <v>6.30488155259532</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.767402132114015</v>
+        <v>4.712604406457532</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1607934641843374</v>
+        <v>0.1604351672686834</v>
       </c>
       <c r="C89">
-        <v>11.89573364762501</v>
+        <v>11.52973916339543</v>
       </c>
       <c r="D89">
-        <v>39.35373364762502</v>
+        <v>39.42173916339544</v>
       </c>
       <c r="E89">
-        <v>22.958</v>
+        <v>23.39200000000001</v>
       </c>
       <c r="F89">
-        <v>37.758</v>
+        <v>38.19200000000001</v>
       </c>
       <c r="G89">
         <v>10.3</v>
@@ -8585,28 +8585,28 @@
         <v>9.84</v>
       </c>
       <c r="M89">
-        <v>2.0880174</v>
+        <v>2.112017600000001</v>
       </c>
       <c r="N89">
-        <v>7.7519826</v>
+        <v>7.727982399999999</v>
       </c>
       <c r="O89">
-        <v>1.744196085</v>
+        <v>1.73879604</v>
       </c>
       <c r="P89">
-        <v>6.007786514999999</v>
+        <v>5.98918636</v>
       </c>
       <c r="Q89">
-        <v>8.167786515</v>
+        <v>8.14918636</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9500572244949032</v>
+        <v>1.022671393905695</v>
       </c>
       <c r="T89">
-        <v>6.30488155259532</v>
+        <v>6.81117967747993</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.712604406457532</v>
+        <v>4.659052083656878</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1604351672686834</v>
+        <v>0.1600768703530294</v>
       </c>
       <c r="C90">
-        <v>11.52973916339543</v>
+        <v>11.16398012090997</v>
       </c>
       <c r="D90">
-        <v>39.42173916339544</v>
+        <v>39.48998012090997</v>
       </c>
       <c r="E90">
-        <v>23.39200000000001</v>
+        <v>23.826</v>
       </c>
       <c r="F90">
-        <v>38.19200000000001</v>
+        <v>38.626</v>
       </c>
       <c r="G90">
         <v>10.3</v>
@@ -8667,28 +8667,28 @@
         <v>9.84</v>
       </c>
       <c r="M90">
-        <v>2.112017600000001</v>
+        <v>2.1360178</v>
       </c>
       <c r="N90">
-        <v>7.727982399999999</v>
+        <v>7.7039822</v>
       </c>
       <c r="O90">
-        <v>1.73879604</v>
+        <v>1.733395995</v>
       </c>
       <c r="P90">
-        <v>5.98918636</v>
+        <v>5.970586205</v>
       </c>
       <c r="Q90">
-        <v>8.14918636</v>
+        <v>8.130586205</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.022671393905695</v>
+        <v>1.108488139572994</v>
       </c>
       <c r="T90">
-        <v>6.81117967747993</v>
+        <v>7.409532006889016</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.659052083656878</v>
+        <v>4.606703183840509</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1600768703530294</v>
+        <v>0.1597185734373753</v>
       </c>
       <c r="C91">
-        <v>11.16398012090997</v>
+        <v>10.79845774497232</v>
       </c>
       <c r="D91">
-        <v>39.48998012090997</v>
+        <v>39.55845774497233</v>
       </c>
       <c r="E91">
-        <v>23.826</v>
+        <v>24.26000000000001</v>
       </c>
       <c r="F91">
-        <v>38.626</v>
+        <v>39.06000000000001</v>
       </c>
       <c r="G91">
         <v>10.3</v>
@@ -8749,28 +8749,28 @@
         <v>9.84</v>
       </c>
       <c r="M91">
-        <v>2.1360178</v>
+        <v>2.160018</v>
       </c>
       <c r="N91">
-        <v>7.7039822</v>
+        <v>7.679981999999999</v>
       </c>
       <c r="O91">
-        <v>1.733395995</v>
+        <v>1.72799595</v>
       </c>
       <c r="P91">
-        <v>5.970586205</v>
+        <v>5.951986049999999</v>
       </c>
       <c r="Q91">
-        <v>8.130586205</v>
+        <v>8.111986049999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.108488139572994</v>
+        <v>1.211468234373753</v>
       </c>
       <c r="T91">
-        <v>7.409532006889016</v>
+        <v>8.127554802179917</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.606703183840509</v>
+        <v>4.555517592908947</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1597185734373753</v>
+        <v>0.1593602765217212</v>
       </c>
       <c r="C92">
-        <v>10.79845774497232</v>
+        <v>10.43317326889643</v>
       </c>
       <c r="D92">
-        <v>39.55845774497233</v>
+        <v>39.62717326889644</v>
       </c>
       <c r="E92">
-        <v>24.26000000000001</v>
+        <v>24.69400000000001</v>
       </c>
       <c r="F92">
-        <v>39.06000000000001</v>
+        <v>39.49400000000001</v>
       </c>
       <c r="G92">
         <v>10.3</v>
@@ -8831,28 +8831,28 @@
         <v>9.84</v>
       </c>
       <c r="M92">
-        <v>2.160018</v>
+        <v>2.184018200000001</v>
       </c>
       <c r="N92">
-        <v>7.679981999999999</v>
+        <v>7.655981799999999</v>
       </c>
       <c r="O92">
-        <v>1.72799595</v>
+        <v>1.722595905</v>
       </c>
       <c r="P92">
-        <v>5.951986049999999</v>
+        <v>5.933385894999999</v>
       </c>
       <c r="Q92">
-        <v>8.111986049999999</v>
+        <v>8.093385894999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.211468234373753</v>
+        <v>1.337332794685792</v>
       </c>
       <c r="T92">
-        <v>8.127554802179917</v>
+        <v>9.005138218646577</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.555517592908947</v>
+        <v>4.505456960019838</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1593602765217212</v>
+        <v>0.1607844796060672</v>
       </c>
       <c r="C93">
-        <v>10.43317326889643</v>
+        <v>9.727436071551516</v>
       </c>
       <c r="D93">
-        <v>39.62717326889644</v>
+        <v>39.35543607155152</v>
       </c>
       <c r="E93">
-        <v>24.69400000000001</v>
+        <v>25.128</v>
       </c>
       <c r="F93">
-        <v>39.49400000000001</v>
+        <v>39.928</v>
       </c>
       <c r="G93">
         <v>10.3</v>
@@ -8913,45 +8913,45 @@
         <v>9.84</v>
       </c>
       <c r="M93">
-        <v>2.184018200000001</v>
+        <v>2.307838400000001</v>
       </c>
       <c r="N93">
-        <v>7.655981799999999</v>
+        <v>7.532161599999999</v>
       </c>
       <c r="O93">
-        <v>1.722595905</v>
+        <v>1.69473636</v>
       </c>
       <c r="P93">
-        <v>5.933385894999999</v>
+        <v>5.83742524</v>
       </c>
       <c r="Q93">
-        <v>8.093385894999999</v>
+        <v>7.99742524</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.337332794685792</v>
+        <v>1.494663495075841</v>
       </c>
       <c r="T93">
-        <v>9.005138218646577</v>
+        <v>10.1021174892299</v>
       </c>
       <c r="U93">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V93">
         <v>0.225</v>
       </c>
       <c r="W93">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y93">
-        <v>4.505456960019838</v>
+        <v>4.263730077461228</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1607844796060672</v>
+        <v>0.1604455576904132</v>
       </c>
       <c r="C94">
-        <v>9.727436071551516</v>
+        <v>9.357763730327775</v>
       </c>
       <c r="D94">
-        <v>39.35543607155152</v>
+        <v>39.41976373032778</v>
       </c>
       <c r="E94">
-        <v>25.128</v>
+        <v>25.56200000000001</v>
       </c>
       <c r="F94">
-        <v>39.928</v>
+        <v>40.36200000000001</v>
       </c>
       <c r="G94">
         <v>10.3</v>
@@ -8995,28 +8995,28 @@
         <v>9.84</v>
       </c>
       <c r="M94">
-        <v>2.307838400000001</v>
+        <v>2.332923600000001</v>
       </c>
       <c r="N94">
-        <v>7.532161599999999</v>
+        <v>7.507076399999999</v>
       </c>
       <c r="O94">
-        <v>1.69473636</v>
+        <v>1.68909219</v>
       </c>
       <c r="P94">
-        <v>5.83742524</v>
+        <v>5.817984209999999</v>
       </c>
       <c r="Q94">
-        <v>7.99742524</v>
+        <v>7.977984209999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.494663495075841</v>
+        <v>1.696945824148761</v>
       </c>
       <c r="T94">
-        <v>10.1021174892299</v>
+        <v>11.51251940855132</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.263730077461228</v>
+        <v>4.217883517488526</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1604455576904132</v>
+        <v>0.1601066357747592</v>
       </c>
       <c r="C95">
-        <v>9.357763730327775</v>
+        <v>8.988302024428464</v>
       </c>
       <c r="D95">
-        <v>39.41976373032778</v>
+        <v>39.48430202442847</v>
       </c>
       <c r="E95">
-        <v>25.56200000000001</v>
+        <v>25.99600000000001</v>
       </c>
       <c r="F95">
-        <v>40.36200000000001</v>
+        <v>40.79600000000001</v>
       </c>
       <c r="G95">
         <v>10.3</v>
@@ -9077,28 +9077,28 @@
         <v>9.84</v>
       </c>
       <c r="M95">
-        <v>2.332923600000001</v>
+        <v>2.3580088</v>
       </c>
       <c r="N95">
-        <v>7.507076399999999</v>
+        <v>7.4819912</v>
       </c>
       <c r="O95">
-        <v>1.68909219</v>
+        <v>1.68344802</v>
       </c>
       <c r="P95">
-        <v>5.817984209999999</v>
+        <v>5.798543179999999</v>
       </c>
       <c r="Q95">
-        <v>7.977984209999999</v>
+        <v>7.958543179999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.696945824148761</v>
+        <v>1.966655596245988</v>
       </c>
       <c r="T95">
-        <v>11.51251940855132</v>
+        <v>13.39305530097987</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.217883517488526</v>
+        <v>4.17301241623865</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1601066357747592</v>
+        <v>0.1597677138591051</v>
       </c>
       <c r="C96">
-        <v>8.988302024428464</v>
+        <v>8.619051990110712</v>
       </c>
       <c r="D96">
-        <v>39.48430202442847</v>
+        <v>39.54905199011072</v>
       </c>
       <c r="E96">
-        <v>25.99600000000001</v>
+        <v>26.43000000000001</v>
       </c>
       <c r="F96">
-        <v>40.79600000000001</v>
+        <v>41.23000000000001</v>
       </c>
       <c r="G96">
         <v>10.3</v>
@@ -9159,28 +9159,28 @@
         <v>9.84</v>
       </c>
       <c r="M96">
-        <v>2.3580088</v>
+        <v>2.383094000000001</v>
       </c>
       <c r="N96">
-        <v>7.4819912</v>
+        <v>7.456905999999999</v>
       </c>
       <c r="O96">
-        <v>1.68344802</v>
+        <v>1.67780385</v>
       </c>
       <c r="P96">
-        <v>5.798543179999999</v>
+        <v>5.779102149999999</v>
       </c>
       <c r="Q96">
-        <v>7.958543179999999</v>
+        <v>7.939102149999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.966655596245988</v>
+        <v>2.344249277182105</v>
       </c>
       <c r="T96">
-        <v>13.39305530097987</v>
+        <v>16.02580555037986</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.17301241623865</v>
+        <v>4.129085969751927</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1597677138591051</v>
+        <v>0.1594287919434511</v>
       </c>
       <c r="C97">
-        <v>8.619051990110712</v>
+        <v>8.250014670440244</v>
       </c>
       <c r="D97">
-        <v>39.54905199011072</v>
+        <v>39.61401467044025</v>
       </c>
       <c r="E97">
-        <v>26.43000000000001</v>
+        <v>26.86400000000001</v>
       </c>
       <c r="F97">
-        <v>41.23000000000001</v>
+        <v>41.66400000000001</v>
       </c>
       <c r="G97">
         <v>10.3</v>
@@ -9241,28 +9241,28 @@
         <v>9.84</v>
       </c>
       <c r="M97">
-        <v>2.383094000000001</v>
+        <v>2.408179200000001</v>
       </c>
       <c r="N97">
-        <v>7.456905999999999</v>
+        <v>7.431820799999999</v>
       </c>
       <c r="O97">
-        <v>1.67780385</v>
+        <v>1.67215968</v>
       </c>
       <c r="P97">
-        <v>5.779102149999999</v>
+        <v>5.759661119999999</v>
       </c>
       <c r="Q97">
-        <v>7.939102149999999</v>
+        <v>7.919661119999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.344249277182105</v>
+        <v>2.910639798586282</v>
       </c>
       <c r="T97">
-        <v>16.02580555037986</v>
+        <v>19.97493092447983</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.129085969751927</v>
+        <v>4.086074657567011</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1594287919434511</v>
+        <v>0.159089870027797</v>
       </c>
       <c r="C98">
-        <v>8.250014670440237</v>
+        <v>7.881191115347299</v>
       </c>
       <c r="D98">
-        <v>39.61401467044024</v>
+        <v>39.67919111534731</v>
       </c>
       <c r="E98">
-        <v>26.864</v>
+        <v>27.29800000000001</v>
       </c>
       <c r="F98">
-        <v>41.664</v>
+        <v>42.09800000000001</v>
       </c>
       <c r="G98">
         <v>10.3</v>
@@ -9323,28 +9323,28 @@
         <v>9.84</v>
       </c>
       <c r="M98">
-        <v>2.4081792</v>
+        <v>2.433264400000001</v>
       </c>
       <c r="N98">
-        <v>7.4318208</v>
+        <v>7.406735599999999</v>
       </c>
       <c r="O98">
-        <v>1.67215968</v>
+        <v>1.66651551</v>
       </c>
       <c r="P98">
-        <v>5.75966112</v>
+        <v>5.740220089999999</v>
       </c>
       <c r="Q98">
-        <v>7.91966112</v>
+        <v>7.900220089999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.910639798586275</v>
+        <v>3.854624000926565</v>
       </c>
       <c r="T98">
-        <v>19.97493092447978</v>
+        <v>26.5568065479797</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.086074657567011</v>
+        <v>4.043950176561165</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.159089870027797</v>
+        <v>0.158750948112143</v>
       </c>
       <c r="C99">
-        <v>7.881191115347299</v>
+        <v>7.512582381683337</v>
       </c>
       <c r="D99">
-        <v>39.67919111534731</v>
+        <v>39.74458238168334</v>
       </c>
       <c r="E99">
-        <v>27.29800000000001</v>
+        <v>27.732</v>
       </c>
       <c r="F99">
-        <v>42.09800000000001</v>
+        <v>42.532</v>
       </c>
       <c r="G99">
         <v>10.3</v>
@@ -9405,28 +9405,28 @@
         <v>9.84</v>
       </c>
       <c r="M99">
-        <v>2.433264400000001</v>
+        <v>2.4583496</v>
       </c>
       <c r="N99">
-        <v>7.406735599999999</v>
+        <v>7.3816504</v>
       </c>
       <c r="O99">
-        <v>1.66651551</v>
+        <v>1.66087134</v>
       </c>
       <c r="P99">
-        <v>5.740220089999999</v>
+        <v>5.72077906</v>
       </c>
       <c r="Q99">
-        <v>7.900220089999999</v>
+        <v>7.88077906</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.854624000926565</v>
+        <v>5.742592405607145</v>
       </c>
       <c r="T99">
-        <v>26.5568065479797</v>
+        <v>39.72055779497956</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.043950176561165</v>
+        <v>4.002685378841154</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.158750948112143</v>
+        <v>0.161097401196489</v>
       </c>
       <c r="C100">
-        <v>7.512582381683337</v>
+        <v>6.630229421985732</v>
       </c>
       <c r="D100">
-        <v>39.74458238168334</v>
+        <v>39.29622942198574</v>
       </c>
       <c r="E100">
-        <v>27.732</v>
+        <v>28.16600000000001</v>
       </c>
       <c r="F100">
-        <v>42.532</v>
+        <v>42.96600000000001</v>
       </c>
       <c r="G100">
         <v>10.3</v>
@@ -9487,129 +9487,47 @@
         <v>9.84</v>
       </c>
       <c r="M100">
-        <v>2.4583496</v>
+        <v>2.633815800000001</v>
       </c>
       <c r="N100">
-        <v>7.3816504</v>
+        <v>7.206184199999999</v>
       </c>
       <c r="O100">
-        <v>1.66087134</v>
+        <v>1.621391445</v>
       </c>
       <c r="P100">
-        <v>5.72077906</v>
+        <v>5.584792755</v>
       </c>
       <c r="Q100">
-        <v>7.88077906</v>
+        <v>7.744792755</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.742592405607145</v>
+        <v>11.40649761964889</v>
       </c>
       <c r="T100">
-        <v>39.72055779497956</v>
+        <v>79.21181153597912</v>
       </c>
       <c r="U100">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V100">
         <v>0.225</v>
       </c>
       <c r="W100">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y100">
-        <v>4.002685378841154</v>
+        <v>3.736024364346207</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.161097401196489</v>
-      </c>
-      <c r="C101">
-        <v>6.630229421985732</v>
-      </c>
-      <c r="D101">
-        <v>39.29622942198574</v>
-      </c>
-      <c r="E101">
-        <v>28.16600000000001</v>
-      </c>
-      <c r="F101">
-        <v>42.96600000000001</v>
-      </c>
-      <c r="G101">
-        <v>10.3</v>
-      </c>
-      <c r="H101">
-        <v>28.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12</v>
-      </c>
-      <c r="K101">
-        <v>2.16</v>
-      </c>
-      <c r="L101">
-        <v>9.84</v>
-      </c>
-      <c r="M101">
-        <v>2.633815800000001</v>
-      </c>
-      <c r="N101">
-        <v>7.206184199999999</v>
-      </c>
-      <c r="O101">
-        <v>1.621391445</v>
-      </c>
-      <c r="P101">
-        <v>5.584792755</v>
-      </c>
-      <c r="Q101">
-        <v>7.744792755</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.40649761964889</v>
-      </c>
-      <c r="T101">
-        <v>79.21181153597912</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.225</v>
-      </c>
-      <c r="W101">
-        <v>0.0475075</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.736024364346207</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
